--- a/data_extactor/batch_10_fa/batch_0009_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0009_fa.xlsx
@@ -503,32 +503,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3M Post-it App | ADP Workforce Now | AJAX | Adobe Acrobat | Adobe ActionScript | Adobe Dreamweaver | Adobe InDesign | Advanced business application programming ABAP | Airtable | Alteryx software | Amazon Elastic Compute Cloud EC2 | Amazon Redshift | Amazon Web Services AWS software | Ansible software | Apache Ant | Apache Cassandra | Apache Groovy | Apache HTTP Server | Apache Hadoop | Apache Hive | Apache Kafka | Apache Maven | Apache Pig | Apache Solr | Apache Spark | Apache Struts | Apache Subversion SVN | Apache Tomcat | Apple macOS | Atlassian Bamboo | Atlassian Confluence | Atlassian JIRA | Backbone.js | Bash | Blackbaud The Raiser's Edge | Blackboard software | C | C# | C++ | Cascading style sheets CSS | Ceridian Dayforce enterprise HCM | Chef | Cisco Webex | Citrix cloud computing software | Common business oriented language COBOL | Customer information control system CICS | نرم‌افزار پایگاه داده | Delphi Technology | Dropbox | Drupal | Dynamic hypertext markup language DHTML | ESRI ArcGIS software | Eclipse IDE | Eko | Elasticsearch | Enterprise JavaBeans | Epic Systems | Ext JS | Extensible hypertext markup language XHTML | Extensible markup language XML | FileMaker Pro | نرم‌افزار حسابداری وجوه | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | Git | GitHub | Go | Google Analytics | Google Angular | Google Docs | Google Drive | Google Meet | Google Slides | Healthcare common procedure coding system HCPCS | Hewlett Packard HP-UX | Hewlett Packard LoadRunner | Hibernate ORM | نرم‌افزار مدیریت منابع انسانی HRMS | Hypertext markup language HTML | IBM Cognos Impromptu | IBM Cognos ReportNet | IBM Domino | IBM InfoSphere DataStage | IBM Notes | IBM Power Systems software | IBM Rational RequisitePro | IBM SPSS Statistics | IBM WebSphere | Information Builders WebFOCUS | نرم‌افزار محیط توسعه یکپارچه IDE | JUnit | JavaScript | JavaScript Object Notation JSON | Job control language JCL | Jupyter Notebook | KornShell | LexisNexis | LinkedIn | Linux | LogMeIn GoToMeeting | MEDITECH software | Marketo Marketing Automation | McAfee | نرم‌افزار کدگذاری وضعیت پزشکی | نرم‌افزار کدگذاری رویه‌های پزشکی | Mentimeter | MicroFocus GroupWise | MicroStrategy | Microsoft .NET Framework | Microsoft ASP.NET | Microsoft ASP.NET Core MVC | Microsoft Access | Microsoft Active Server Pages ASP | Microsoft ActiveX | Microsoft Azure software | Microsoft Business Intelligence BI | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Excel | Microsoft Exchange | نرم‌افزار Microsoft Office | Microsoft OneNote | Microsoft Outlook | Microsoft Power BI | Microsoft PowerPoint | Microsoft PowerShell | Microsoft Project | Microsoft Publisher | Microsoft SQL Server | Microsoft SQL Server Integration Services SSIS | Microsoft SQL Server Reporting Services SSRS | Microsoft SharePoint | Microsoft Team Foundation Server | Microsoft Teams | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic Scripting Edition VBScript | Microsoft Visual Basic for Applications VBA | Microsoft Visual Studio | Microsoft Windows | Microsoft Word | Minitab | MongoDB | MySQL | Nagios | NetSuite ERP | NoSQL | Node.js | NortonLifeLock cybersecurity software | Oracle Agile Product Lifecycle Management PLM | Oracle Business Intelligence Enterprise Edition | Oracle Business Intelligence Publisher | Oracle Database | Oracle E-Business Suite Financials | Oracle Eloqua | Oracle Fusion Applications | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle JDBC | Oracle Java | Oracle JavaServer Pages JSP | Oracle PL/SQL | Oracle PeopleSoft | Oracle PeopleSoft Financials | Oracle Primavera Enterprise Project Portfolio Management | Oracle Solaris | Oracle Taleo | Oracle WebLogic Server | PHP | Perforce Helix software | Perl | PostgreSQL | Puppet | Python | Qlik Tech QlikView | Quest Erwin Data Modeler | R | Red Hat Enterprise Linux | Red Hat WildFly | نرم‌افزار مدیریت پایگاه داده رابطه‌ای | Ruby | Ruby on Rails | SAP Business Objects | SAP Crystal Reports | نرم‌افزار SAP | SAS | Sage 50 Accounting | Salesforce Visualforce | نرم‌افزار Salesforce | Scala | Screencastify | Selenium | Shell script | Skype | نرم‌افزار تعاملی Slido | SmugMug Flickr | Splunk Enterprise | Spring Framework | StataCorp Stata | Structured query language SQL | نرم‌افزار کنترل نظارتی و جمع‌آوری داده SCADA | Swift | Tableau | نرم‌افزار مالیاتی | Teradata Database | The MathWorks MATLAB | Transact-SQL | Trimble SketchUp Pro | UNIX | Ubuntu | Unified modeling language UML | VMware | Veritas NetBackup | نرم‌افزار شبکه خصوصی مجازی VPN | نرم‌افزار مرورگر وب | Wireshark | jQuery</t>
+          <t>3M Post-it App | ADP Workforce Now | AJAX | Adobe Acrobat | Adobe ActionScript | Adobe Dreamweaver | Adobe InDesign | برنامه‌نویسی پیشرفته برنامه‌های تجاری ABAP | Airtable | نرم‌افزار Alteryx | Amazon Elastic Compute Cloud EC2 | Amazon Redshift | نرم‌افزار Amazon Web Services AWS | نرم‌افزار Ansible | Apache Ant | Apache Cassandra | Apache Groovy | Apache HTTP Server | Apache Hadoop | Apache Hive | Apache Kafka | Apache Maven | Apache Pig | Apache Solr | Apache Spark | Apache Struts | Apache Subversion SVN | Apache Tomcat | Apple macOS | Atlassian Bamboo | Atlassian Confluence | Atlassian JIRA | Backbone.js | Bash | Blackbaud The Raiser's Edge | نرم‌افزار Blackboard | C | C# | C++ | برگه‌های سبک آبشاری CSS | Ceridian Dayforce enterprise HCM | Chef | Cisco Webex | نرم‌افزار رایانش ابری Citrix | زبان مشترک تجاری COBOL | سیستم کنترل اطلاعات مشتری CICS | نرم‌افزار پایگاه داده | Delphi Technology | Dropbox | Drupal | زبان نشانه‌گذاری ابرمتن پویا DHTML | نرم‌افزار ESRI ArcGIS | Eclipse IDE | Eko | Elasticsearch | Enterprise JavaBeans | Epic Systems | Ext JS | زبان نشانه‌گذاری ابرمتن توسعه‌پذیر XHTML | زبان نشانه‌گذاری توسعه‌پذیر XML | FileMaker Pro | نرم‌افزار حسابداری صندوق | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | Git | GitHub | Go | Google Analytics | Google Angular | Google Docs | Google Drive | Google Meet | Google Slides | سیستم کدگذاری رویه‌های رایج مراقبت‌های بهداشتی HCPCS | Hewlett Packard HP-UX | Hewlett Packard LoadRunner | Hibernate ORM | نرم‌افزار مدیریت منابع انسانی HRMS | زبان نشانه‌گذاری ابرمتن HTML | IBM Cognos Impromptu | IBM Cognos ReportNet | IBM Domino | IBM InfoSphere DataStage | IBM Notes | نرم‌افزار IBM Power Systems | IBM Rational RequisitePro | IBM SPSS Statistics | IBM WebSphere | Information Builders WebFOCUS | نرم‌افزار محیط توسعه یکپارچه IDE | JUnit | JavaScript | JavaScript Object Notation JSON | زبان کنترل کار JCL | Jupyter Notebook | KornShell | LexisNexis | LinkedIn | Linux | LogMeIn GoToMeeting | نرم‌افزار MEDITECH | Marketo Marketing Automation | McAfee | نرم‌افزار کدگذاری شرایط پزشکی | نرم‌افزار کدگذاری رویه‌های پزشکی | Mentimeter | MicroFocus GroupWise | MicroStrategy | Microsoft .NET Framework | Microsoft ASP.NET | Microsoft ASP.NET Core MVC | Microsoft Access | Microsoft Active Server Pages ASP | Microsoft ActiveX | نرم‌افزار Microsoft Azure | Microsoft Business Intelligence BI | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Excel | Microsoft Exchange | نرم‌افزار Microsoft Office | Microsoft OneNote | Microsoft Outlook | Microsoft Power BI | Microsoft PowerPoint | Microsoft PowerShell | Microsoft Project | Microsoft Publisher | Microsoft SQL Server | Microsoft SQL Server Integration Services SSIS | Microsoft SQL Server Reporting Services SSRS | Microsoft SharePoint | Microsoft Team Foundation Server | Microsoft Teams | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic Scripting Edition VBScript | Microsoft Visual Basic for Applications VBA | Microsoft Visual Studio | Microsoft Windows | Microsoft Word | Minitab | MongoDB | MySQL | Nagios | NetSuite ERP | NoSQL | Node.js | نرم‌افزار امنیت سایبری NortonLifeLock | Oracle Agile Product Lifecycle Management PLM | Oracle Business Intelligence Enterprise Edition | Oracle Business Intelligence Publisher | Oracle Database | Oracle E-Business Suite Financials | Oracle Eloqua | Oracle Fusion Applications | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle JDBC | Oracle Java | Oracle JavaServer Pages JSP | Oracle PL/SQL | Oracle PeopleSoft | Oracle PeopleSoft Financials | Oracle Primavera Enterprise Project Portfolio Management | Oracle Solaris | Oracle Taleo | Oracle WebLogic Server | PHP | نرم‌افزار Perforce Helix | Perl | PostgreSQL | Puppet | Python | Qlik Tech QlikView | Quest Erwin Data Modeler | R | Red Hat Enterprise Linux | Red Hat WildFly | نرم‌افزار مدیریت پایگاه داده رابطه‌ای | Ruby | Ruby on Rails | SAP Business Objects | SAP Crystal Reports | نرم‌افزار SAP | SAS | Sage 50 Accounting | Salesforce Visualforce | نرم‌افزار Salesforce | Scala | Screencastify | Selenium | Shell script | Skype | نرم‌افزار تعاملی Slido | SmugMug Flickr | Splunk Enterprise | Spring Framework | StataCorp Stata | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | Swift | Tableau | نرم‌افزار مالیاتی | Teradata Database | The MathWorks MATLAB | Transact-SQL | Trimble SketchUp Pro | UNIX | Ubuntu | زبان مدل‌سازی یکپارچه UML | VMware | Veritas NetBackup | نرم‌افزار شبکه خصوصی مجازی VPN | نرم‌افزار مرورگر وب | Wireshark | jQuery</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | صحبت کردن | نوشتن | نظارت | یادگیری فعال | راهبردهای یادگیری | ریاضیات</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | مدیریت و اداره | خدمات مشتری و شخصی | ریاضیات | آموزش و پرورش | رایانه و الکترونیک | اقتصاد و حسابداری | پرسنل و منابع انسانی | قانون و دولت | فروش و بازاریابی | روان‌شناسی | ارتباطات و رسانه | جامعه‌شناسی و مردم‌شناسی</t>
+          <t>زبان انگلیسی | مدیریت و اداره | خدمات مشتری و شخصی | ریاضیات | آموزش و پرورش | رایانه و الکترونیک | اقتصاد و حسابداری | پرسنل و منابع انسانی | قانون و دولت | فروش و بازاریابی | روان‌شناسی | ارتباطات و رسانه | جامعه‌شناسی و انسان‌شناسی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شنیداری | درک نوشتاری | بیان شفاهی | حساسیت به مسئله | بیان نوشتاری | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | روانی ایده‌ها | نظم‌دهی اطلاعات | دید نزدیک | انعطاف‌پذیری دسته‌بندی | خلاقیت | توجه انتخابی | انعطاف‌پذیری بستار | استدلال ریاضی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | بیان کتبی | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | روانی ایده‌ها | ترتیب‌دهی اطلاعات | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | اصالت | توجه انتخابی | انعطاف‌پذیری بستار | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | بحث‌های حضوری با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | محیط داخلی، دارای کنترل محیطی | تماس با دیگران | صرف زمان برای نشستن | آزادی در تصمیم‌گیری | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا صحیح بودن | فشار زمانی | نامه‌ها و یادداشت‌های مکتوب | تناوب تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | نتایج کاری و خروجی‌های سایر کارکنان | سطح رقابت</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | محیط داخلی، دارای کنترل شرایط محیطی | ارتباط با دیگران | صرف زمان برای نشستن | آزادی در تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا درست بودن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | فراوانی تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | پیامدهای کاری و نتایج سایر کارکنان | سطح رقابت</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری | برنامه‌ریزان تداوم کسب‌وکار | تحلیل‌گران هوش تجاری | مدرسان کسب‌وکار، پس از متوسطه | مدیران ارشد اجرایی | مدیران انطباق | تحلیل‌گران سیستم‌های رایانه‌ای | مدیران سیستم‌های رایانه‌ای و اطلاعاتی | دانشمندان داده | متخصصان مدیریت اسناد | متخصصان ریسک مالی | سرپرستان خط اول کارکنان اداری و پشتیبانی دفتری | فناوران اطلاعات سلامت و ثبت‌کنندگان پزشکی | روان‌شناسان صنعتی-سازمانی | مدیران پروژه فناوری اطلاعات | تحلیل‌گران تحقیقات بازار و متخصصان بازاریابی | تحلیل‌گران تحقیق در عملیات | متخصصان مدیریت پروژه | دستیاران آماری | مدیران آموزش و توسعه</t>
+          <t>مدیران خدمات اداری | برنامه‌ریزان تداوم کسب‌وکار | تحلیلگران هوش تجاری | اساتید کسب‌وکار، پس از متوسطه | مدیران ارشد اجرایی | مدیران انطباق | تحلیلگران سیستم‌های کامپیوتری | مدیران کامپیوتر و سیستم‌های اطلاعاتی | دانشمندان داده | متخصصان مدیریت اسناد | متخصصان ریسک مالی | سرپرستان خط اول کارکنان دفتری و پشتیبانی اداری | فن‌آوران اطلاعات سلامت و ثبت‌کنندگان پزشکی | روان‌شناسان صنعتی-سازمانی | مدیران پروژه فناوری اطلاعات | تحلیل‌گران تحقیقات بازار و متخصصان بازاریابی | تحلیل‌گران تحقیق در عملیات | متخصصان مدیریت پروژه | دستیاران آماری | مدیران آموزش و توسعه</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -560,12 +560,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Active Network EventRegister | نرم‌افزار Adobe Creative Cloud | Adobe InDesign | Adobe Photoshop | Blackbaud The Raiser's Edge | Convention Industry Council CIC APEX Toolbox | Dean Evans &amp; Associates EMS Professional | Delphi Discovery | Delphi Technology | ESRI ArcGIS software | نرم‌افزار مدیریت رویداد | نرم‌افزار عملیات رویدادها | Facebook | FileMaker Pro | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | Google Docs | Google Drive | GruupMeet | Hypertext markup language HTML | IBM Lotus Notes | نرم‌افزار اتوماسیون بازاریابی Lenos | LinkedIn | LogMeIn GoToMeeting | LogMeIn GoToWebinar | Marketo Marketing Automation | MeetingMatrix International | MemberClicks COMPLETE | Mentimeter | Microsoft Access | Microsoft Dynamics | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft Word | NSF Hospitality Rendezvous Events | Oracle Eloqua | Oracle Primavera Enterprise Project Portfolio Management | ParentSquare | Planstone | SmugMug Flickr | سایت‌های رسانه‌های اجتماعی | Trimble SketchUp Pro | نرم‌افزار مرورگر وب</t>
+          <t>Active Network EventRegister | نرم‌افزار Adobe Creative Cloud | Adobe InDesign | Adobe Photoshop | Blackbaud The Raiser's Edge | Convention Industry Council CIC APEX Toolbox | Dean Evans &amp; Associates EMS Professional | Delphi Discovery | Delphi Technology | نرم‌افزار ESRI ArcGIS | نرم‌افزار مدیریت رویداد | نرم‌افزار عملیات رویدادها | Facebook | FileMaker Pro | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | Google Docs | Google Drive | GruupMeet | زبان نشانه‌گذاری ابرمتن HTML | IBM Lotus Notes | نرم‌افزار اتوماسیون بازاریابی Lenos | LinkedIn | LogMeIn GoToMeeting | LogMeIn GoToWebinar | Marketo Marketing Automation | MeetingMatrix International | MemberClicks COMPLETE | Mentimeter | Microsoft Access | Microsoft Dynamics | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft Word | NSF Hospitality Rendezvous Events | Oracle Eloqua | Oracle Primavera Enterprise Project Portfolio Management | ParentSquare | Planstone | SmugMug Flickr | سایت‌های رسانه‌های اجتماعی | Trimble SketchUp Pro | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | درک مطلب | صحبت کردن | تفکر انتقادی | نوشتن | نظارت | یادگیری فعال</t>
+          <t>گوش دادن فعال | درک مطلب | سخن گفتن | تفکر انتقادی | نگارش | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -575,17 +575,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شنیداری | درک نوشتاری | بیان شفاهی | بیان نوشتاری | تشخیص گفتار | حساسیت به مسئله | استدلال قیاسی | وضوح گفتار | روانی ایده‌ها | دید نزدیک | خلاقیت | استدلال استقرایی | نظم‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | دید دور | توجه انتخابی | اشتراک زمانی | تجسم | استدلال ریاضی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | تشخیص گفتار | حساسیت به مسئله | استدلال قیاسی | وضوح گفتار | روانی ایده‌ها | بینایی نزدیک | اصالت | استدلال استقرایی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | بینایی دور | توجه انتخابی | تقسیم توجه | تجسم | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>مکالمات تلفنی | بحث‌های حضوری با افراد و درون تیم‌ها | تماس با دیگران | ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | تعامل با مشتریان خارجی یا عموم مردم | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | فشار زمانی | آزادی در تصمیم‌گیری | تناوب تصمیم‌گیری | محیط داخلی، دارای کنترل محیطی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | نامه‌ها و یادداشت‌های مکتوب | اهمیت دقیق یا صحیح بودن | نتایج کاری و خروجی‌های سایر کارکنان | سطح رقابت | مجاورت فیزیکی | صرف زمان برای انجام حرکات تکراری | صرف زمان برای نشستن | قرار گرفتن در معرض صداها، سطوح نویز که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | موقعیت‌های تعارض</t>
+          <t>مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | تعامل با مشتریان خارجی یا عموم مردم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فشار زمانی | آزادی در تصمیم‌گیری | فراوانی تصمیم‌گیری | محیط داخلی، دارای کنترل شرایط محیطی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | نامه‌ها و یادداشت‌های کتبی | اهمیت دقیق یا درست بودن | پیامدهای کاری و نتایج سایر کارکنان | سطح رقابت | نزدیکی فیزیکی | صرف زمان برای انجام حرکات تکراری | صرف زمان برای نشستن | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | موقعیت‌های تعارض</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری | نمایندگان و مدیران تجاری هنرمندان، اجراکنندگان و ورزشکاران | برنامه‌ریزان تداوم کسب‌وکار | منشی‌های اجرایی و دستیاران اداری اجرایی | سرپرستان خط اول کارکنان سرگرمی و تفریحی، به جز خدمات قمار | سرپرستان خط اول کارکنان فروش غیرخرده‌فروشی | سرپرستان خط اول کارکنان اداری و پشتیبانی دفتری | جمع‌آوری‌کنندگان کمک مالی | مدیران جمع‌آوری کمک مالی | مدیران پروژه فناوری اطلاعات | تدارکات‌چی‌ها | تحلیل‌گران مدیریت | مدیران برنامه‌سازی رسانه | متخصصان مدیریت پروژه | مدیران روابط عمومی | متخصصان روابط عمومی | کارکنان تفریحی | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و مسافرتی | منشی‌ها و دستیاران اداری، به جز حقوقی، پزشکی و اجرایی | مدیران خدمات اجتماعی و جامعه</t>
+          <t>مدیران خدمات اداری | نمایندگان و مدیران تجاری هنرمندان، اجراکنندگان و ورزشکاران | برنامه‌ریزان تداوم کسب‌وکار | منشی‌های اجرایی و دستیاران اداری اجرایی | سرپرستان خط اول کارگران سرگرمی و تفریح، به جز خدمات قمار | سرپرستان رده اول کارکنان فروش غیرخرده‌فروشی | سرپرستان خط اول کارکنان دفتری و پشتیبانی اداری | جمع‌آوری‌کنندگان کمک مالی | مدیران جمع‌آوری کمک‌های مالی | مدیران پروژه فناوری اطلاعات | لجستیسین‌ها | تحلیل‌گران مدیریت | مدیران برنامه‌ریزی رسانه | متخصصان مدیریت پروژه | مدیران روابط عمومی | متخصصان روابط عمومی | کارکنان تفریحات | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | منشی‌ها و دستیاران اداری، به جز حقوقی، پزشکی و اجرایی | مدیران خدمات اجتماعی و جامعه</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -617,12 +617,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Adobe PageMaker | AudienceView Ticketing | Blackbaud Luminate CRM | Blackbaud The Raiser's Edge | Blackbaud eTapestry | Constant Contact | Corel CorelDraw Graphics Suite | نرم‌افزار پایگاه داده | نرم‌افزار ایمیل | Facebook | FileMaker Pro | Foundatino Directory Online (FDO) | Microsoft Dynamics | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Publisher | Microsoft Word | SAP BusinessObjects Crystal Reports | نرم‌افزار Salesforce | SofterWare DonorPerfect | Structured query language SQL | Tessitura Network Tessitura Software | Twitter | WealthEngine Findwealth | نرم‌افزار مرورگر وب</t>
+          <t>Adobe PageMaker | AudienceView Ticketing | Blackbaud Luminate CRM | Blackbaud The Raiser's Edge | Blackbaud eTapestry | Constant Contact | Corel CorelDraw Graphics Suite | نرم‌افزار پایگاه داده | نرم‌افزار ایمیل | Facebook | FileMaker Pro | Foundatino Directory Online (FDO) | Microsoft Dynamics | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Publisher | Microsoft Word | SAP BusinessObjects Crystal Reports | نرم‌افزار Salesforce | SofterWare DonorPerfect | زبان پرس‌وجوی ساختاریافته SQL | Tessitura Network Tessitura Software | Twitter | WealthEngine Findwealth | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>صحبت کردن | نوشتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | یادگیری فعال | نظارت | ریاضیات</t>
+          <t>سخن گفتن | نگارش | گوش دادن فعال | درک مطلب | تفکر انتقادی | یادگیری فعال | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -632,17 +632,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>بیان شفاهی | وضوح گفتار | درک شنیداری | درک نوشتاری | بیان نوشتاری | تشخیص گفتار | استدلال استقرایی | استدلال قیاسی | روانی ایده‌ها | دید نزدیک | حساسیت به مسئله | نظم‌دهی اطلاعات | خلاقیت | انعطاف‌پذیری دسته‌بندی | تسهیلات عددی | استدلال ریاضی</t>
+          <t>بیان شفاهی | وضوح گفتار | درک شفاهی | درک کتبی | بیان کتبی | تشخیص گفتار | استدلال استقرایی | استدلال قیاسی | روانی ایده‌ها | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | اصالت | انعطاف‌پذیری دسته‌بندی | توانایی عددی | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>بحث‌های حضوری با افراد و درون تیم‌ها | ایمیل | مکالمات تلفنی | تعامل با مشتریان خارجی یا عموم مردم | تماس با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | نامه‌ها و یادداشت‌های مکتوب | آزادی در تصمیم‌گیری | صرف زمان برای نشستن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | محیط داخلی، دارای کنترل محیطی | تناوب تصمیم‌گیری | فشار زمانی | اهمیت دقیق یا صحیح بودن | سطح رقابت</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ایمیل | مکالمات تلفنی | تعامل با مشتریان خارجی یا عموم مردم | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | نامه‌ها و یادداشت‌های کتبی | آزادی در تصمیم‌گیری | صرف زمان برای نشستن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | محیط داخلی، دارای کنترل شرایط محیطی | فراوانی تصمیم‌گیری | فشار زمانی | اهمیت دقیق یا درست بودن | سطح رقابت</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>نمایندگان فروش تبلیغات | مدیران تبلیغات و ترویج | نمایندگان و مدیران تجاری هنرمندان، اجراکنندگان و ورزشکاران | تحلیل‌گران بودجه | مدیران ارشد اجرایی | مشاوران اعتباری | مدیران آموزش، پس از متوسطه | مدیران مالی | مدیران جمع‌آوری کمک مالی | مدیران پروژه فناوری اطلاعات | مدیران صندوق سرمایه‌گذاری | تحلیل‌گران مدیریت | تحلیل‌گران تحقیقات بازار و متخصصان بازاریابی | مدیران بازاریابی | برنامه‌ریزان جلسات، همایش‌ها و رویدادها | مشاوران مالی شخصی | مدیران روابط عمومی | متخصصان روابط عمومی | مدیران فروش | مدیران خدمات اجتماعی و جامعه</t>
+          <t>نمایندگان فروش تبلیغات | مدیران تبلیغات و ترویج | نمایندگان و مدیران تجاری هنرمندان، اجراکنندگان و ورزشکاران | تحلیلگران بودجه | مدیران ارشد اجرایی | مشاوران اعتبار | مدیران آموزشی، پس از متوسطه | مدیران مالی | مدیران جمع‌آوری کمک‌های مالی | مدیران پروژه فناوری اطلاعات | مدیران صندوق سرمایه‌گذاری | تحلیل‌گران مدیریت | تحلیل‌گران تحقیقات بازار و متخصصان بازاریابی | مدیران بازاریابی | برنامه‌ریزان جلسات، همایش‌ها و رویدادها | مشاوران مالی شخصی | مدیران روابط عمومی | متخصصان روابط عمومی | مدیران فروش | مدیران خدمات اجتماعی و جامعه</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ADP Enterprise eTIME | ADP Workforce Now | Actuarial Systems Corporation AIM | Actuarial Systems Corporation Compliance Testing System | Actuarial Systems Corporation DV Direct | Actuarial Systems Corporation Defined Benefit System | Actuarial Systems Corporation Document Generation and Management System | Apex Business Software iBenefits | Ascentis Employee Self-Service | Ascentis HR | BEMAS PayDirect | Bargaining Power | BenAssist | Benaissance COBRApoint | BeneLink Connect | BeneXL Technologies Pension Administration System | Benefit Plan Systems Corporation The Plan Administrator | Benefit Software Fringe Facts | BenefitFocus HR in Touch | Benelogic | Byrne Software Technologies Visual HCS | Callidus TrueComp | Ceridian Dayforce enterprise HCM | Clayton Wallis CompGeo Online Professional Forecast Library | DataPath dpiSuite | نرم‌افزار سیستم مدیریت اسناد | Ebenefits Solutions Benefits Management | نرم‌افزار سلف‌سرویس کارکنان | Halogen eCompensation | Healthcare common procedure coding system HCPCS | سیستم اطلاعات منابع انسانی (HRIS) | نرم‌افزار مدیریت منابع انسانی HRMS | Humanic Design Employmee Self-Service | Humanic Design Human Resources Management System | IBM Cognos | IBM Cognos Impromptu | IBM SPSS Statistics | نرم‌افزار سیستم مدیریت مشوق | InfinityHR | Kronos Workforce Timekeeper | Lawson ERP | LinkedIn | Lynchval Systems Lvadmin | Lynchval Systems Lvval | Lynchval Systems Lvxact | نرم‌افزار کدگذاری وضعیت پزشکی | نرم‌افزار کدگذاری رویه‌های پزشکی | MicroStrategy | Microsoft Access | Microsoft Dynamics | Microsoft Excel | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft SharePoint | Microsoft Visual Basic | Microsoft Word | NPKTools Comp Analytics | NPKTools CompXpert | O*NET OnLine | OnQue Technologies COBRA OnOne | Oracle E-Business Suite Human Resources Management System | Oracle Fusion Applications | Oracle HRIS | Oracle PeopleSoft | Oracle Taleo | نرم‌افزار برنامه‌ریزی پروژه | نرم‌افزار مدیریت پایگاه داده رابطه‌ای | SAP Crystal Reports | SAP ERP Human Capital Management | نرم‌افزار SAP | SAS | SBC Systems Benefits Workstation | Sage HRMS | Salary.com | Stroud &amp; Associates Employee Benefits Administration System | Structured query language SQL | Survey Sense | Transcend Technologies Group benefitsCONNECT | Travis Software TravisFlex | Ultimate Software UltiPro Workplace | VUE Benefits Manager | VUE Compensation Management | Vebnet FIX&amp;FLEX | Virtual Benefits Administrator | Vitech Systems Group V3 Benefits Administration System | Watson Wyatt CompQuest On-Line | Watson Wyatt Global Grading System | Watson Wyatt Reward | Workday software | Workscape Outsourced Employee Benefits Administration | Xactly Compel</t>
+          <t>ADP Enterprise eTIME | ADP Workforce Now | Actuarial Systems Corporation AIM | Actuarial Systems Corporation Compliance Testing System | Actuarial Systems Corporation DV Direct | Actuarial Systems Corporation Defined Benefit System | Actuarial Systems Corporation Document Generation and Management System | Apex Business Software iBenefits | Ascentis Employee Self-Service | Ascentis HR | BEMAS PayDirect | Bargaining Power | BenAssist | Benaissance COBRApoint | BeneLink Connect | BeneXL Technologies Pension Administration System | Benefit Plan Systems Corporation The Plan Administrator | Benefit Software Fringe Facts | BenefitFocus HR in Touch | Benelogic | Byrne Software Technologies Visual HCS | Callidus TrueComp | Ceridian Dayforce enterprise HCM | Clayton Wallis CompGeo Online Professional Forecast Library | DataPath dpiSuite | نرم‌افزار سیستم مدیریت اسناد | Ebenefits Solutions Benefits Management | نرم‌افزار سلف‌سرویس کارکنان | Halogen eCompensation | سیستم کدگذاری رویه‌های رایج مراقبت‌های بهداشتی HCPCS | سیستم اطلاعات منابع انسانی (HRIS) | نرم‌افزار مدیریت منابع انسانی HRMS | Humanic Design Employmee Self-Service | Humanic Design Human Resources Management System | IBM Cognos | IBM Cognos Impromptu | IBM SPSS Statistics | نرم‌افزار سیستم مدیریت مشوق | InfinityHR | Kronos Workforce Timekeeper | Lawson ERP | LinkedIn | Lynchval Systems Lvadmin | Lynchval Systems Lvval | Lynchval Systems Lvxact | نرم‌افزار کدگذاری شرایط پزشکی | نرم‌افزار کدگذاری رویه‌های پزشکی | MicroStrategy | Microsoft Access | Microsoft Dynamics | Microsoft Excel | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft SharePoint | Microsoft Visual Basic | Microsoft Word | NPKTools Comp Analytics | NPKTools CompXpert | O*NET OnLine | OnQue Technologies COBRA OnOne | Oracle E-Business Suite Human Resources Management System | Oracle Fusion Applications | Oracle HRIS | Oracle PeopleSoft | Oracle Taleo | نرم‌افزار برنامه‌ریزی پروژه | نرم‌افزار مدیریت پایگاه داده رابطه‌ای | SAP Crystal Reports | SAP ERP Human Capital Management | نرم‌افزار SAP | SAS | SBC Systems Benefits Workstation | Sage HRMS | Salary.com | Stroud &amp; Associates Employee Benefits Administration System | زبان پرس‌وجوی ساختاریافته SQL | Survey Sense | Transcend Technologies Group benefitsCONNECT | Travis Software TravisFlex | Ultimate Software UltiPro Workplace | VUE Benefits Manager | VUE Compensation Management | Vebnet FIX&amp;FLEX | Virtual Benefits Administrator | Vitech Systems Group V3 Benefits Administration System | Watson Wyatt CompQuest On-Line | Watson Wyatt Global Grading System | Watson Wyatt Reward | نرم‌افزار Workday | Workscape Outsourced Employee Benefits Administration | Xactly Compel</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش دادن فعال | صحبت کردن | تفکر انتقادی | نوشتن | یادگیری فعال | ریاضیات | نظارت</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | تفکر انتقادی | نگارش | یادگیری فعال | ریاضیات | نظارت</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -689,17 +689,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شنیداری | درک نوشتاری | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | بیان نوشتاری | نظم‌دهی اطلاعات | دید نزدیک | تشخیص گفتار | استدلال ریاضی | توجه انتخابی | انعطاف‌پذیری بستار | خلاقیت | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | بیان کتبی | ترتیب‌دهی اطلاعات | بینایی نزدیک | تشخیص گفتار | استدلال ریاضی | توجه انتخابی | انعطاف‌پذیری بستار | اصالت | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | صرف زمان برای نشستن | بحث‌های حضوری با افراد و درون تیم‌ها | اهمیت دقیق یا صحیح بودن | محیط داخلی، دارای کنترل محیطی | تماس با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | تناوب تصمیم‌گیری | فشار زمانی | آزادی در تصمیم‌گیری | اهمیت تکرار وظایف مشابه | نامه‌ها و یادداشت‌های مکتوب</t>
+          <t>ایمیل | مکالمات تلفنی | صرف زمان برای نشستن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | محیط داخلی، دارای کنترل شرایط محیطی | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | فراوانی تصمیم‌گیری | فشار زمانی | آزادی در تصمیم‌گیری | اهمیت تکرار وظایف یکسان | نامه‌ها و یادداشت‌های کتبی</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | مدیران خدمات اداری | تحلیل‌گران بودجه | مدیران ارشد اجرایی | مدیران جبران خدمات و مزایا | مدیران انطباق | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | نمایندگان و افسران فرصت‌های برابر | بازرسان مالی | مدیران مالی | سرپرستان خط اول کارکنان اداری و پشتیبانی دفتری | دستیاران منابع انسانی، به جز حقوق و دستمزد و زمان‌سنجی | مدیران منابع انسانی | متخصصان منابع انسانی | منشی‌های پردازش ادعاها و سیاست‌های بیمه | متخصصان روابط کار | تحلیل‌گران مدیریت | مدیران خدمات بهداشتی و درمانی | منشی‌های حقوق و دستمزد و زمان‌سنجی | مدیران خدمات اجتماعی و جامعه</t>
+          <t>حسابداران و حسابرسان | مدیران خدمات اداری | تحلیلگران بودجه | مدیران ارشد اجرایی | مدیران جبران خدمات و مزایا | مدیران انطباق | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | نمایندگان و افسران فرصت‌های برابر | بازرسان مالی | مدیران مالی | سرپرستان خط اول کارکنان دفتری و پشتیبانی اداری | دستیاران منابع انسانی، به جز حقوق و دستمزد و ثبت زمان | مدیران منابع انسانی | متخصصان منابع انسانی | کارمندان پردازش بیمه و بیمه‌نامه | متخصصان روابط کار | تحلیل‌گران مدیریت | مدیران خدمات پزشکی و بهداشتی | کارمندان حقوق و دستمزد و ثبت زمان | مدیران خدمات اجتماعی و جامعه</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -731,12 +731,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Adobe Acrobat | Adobe ActionScript | Adobe After Effects | Adobe Authorware | Adobe Captivate | نرم‌افزار Adobe Creative Cloud | Adobe Dreamweaver | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Adobe Presenter | Advanced business application programming ABAP | Alchemy Systems SISTEM | Apache Struts | Apple Final Cut Pro | Articulate Rapid E-Learning Studio | Backbone.js | سیستم مدیریت یادگیری Beeline LMS | Blackbaud The Raiser's Edge | Blackboard software | Blatant Media Absorb LMS | Brainshark Rapid Learning | Cisco Webex | Citrix cloud computing software | Cobent Learning and Compliance Suite LCS | Common Curriculum | سیستم مدیریت یادگیری Computer Generated Solutions | نرم‌افزار پایگاه داده | Django | Drupal | EZ LCMS | Eedo Knowledgeware Eedo Force Ten | ElearningForce JoomlaLMS | Epic Systems | FileMaker Pro | FlexTraining Total e-Learning Solution | G-Cube Solutions Wizdom Web LMS | GeoMetrix Data Systems Training Partner | Google Drive | Google Meet | Google Sites | Google Slides | HP Trim | Halogen eLMS | نرم‌افزار مدیریت منابع انسانی HRMS | Hypertext markup language HTML | IBM Notes | IBM SPSS Statistics | ICS Learning Group Inquisiq EX | Ikonami AT-Learning Tool | Inspired eLearning iLMS | Intelladon Enterprise Knowledge Platform EKP | Intelligent Information Conversion Technologies MeritScholar | Intellum Rollbook | Interwoven software | JavaScript | Kahoot! | Learn HQ Activate LMS | سیستم مدیریت یادگیری LMS | LogMeIn GoToMeeting | LogMeIn GoToWebinar | Medworxx Learning Management System | Mentimeter | Microsoft Access | Microsoft Dynamics | Microsoft Excel | Microsoft NetMeeting | نرم‌افزار Microsoft Office | Microsoft OneNote | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft SharePoint | Microsoft Visio | Microsoft Word | Moodle | MySQL | Mzinga On-Demand Learning Suite | NetDimensions Enterprise Knowledge Platform EKP | OnPoint Digital OnPoint Learning &amp; Performance Suite | Operitel LearnFlex | Oracle Business Intelligence Enterprise Edition | Oracle PL/SQL | Oracle PeopleSoft | Oracle PeopleSoft Financials | Oracle Solaris | Oracle Taleo | Oracle WebLogic Server | PHP | PRO-ductivity Systems Compliance Training Manager Web | Pathlore LMS | Plateau Learning Management System LMS | Poll Everywhere | Prezi | Qarbon ViewletBuilder Professional | RISC Virtual Training Assistant | Right Reason Technologies RightTrack | نرم‌افزار SAP | Screencast-O-Matic | SkillSoft SkillPort | SmugMug Flickr | SumTotal Systems ToolBook | SumTotal Systems TotalLMS | Telania eLeaP Learning Management System LMS/LCMS | The Human Equation InSite LMS | TrainCaster LMS | TrainOnTrack Learning Management System LMS | Upside Learning UpsideLMS | WeVideo | نرم‌افزار مرورگر وب | Xerceo Learn | سیستم مدیریت محتوای یادگیری Xyleme LCMS | Ziiva Prosperity LMS | Zoom | dominKnow Learning Center | techniques.org knowledgeWorks LMS</t>
+          <t>Adobe Acrobat | Adobe ActionScript | Adobe After Effects | Adobe Authorware | Adobe Captivate | نرم‌افزار Adobe Creative Cloud | Adobe Dreamweaver | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Adobe Presenter | برنامه‌نویسی پیشرفته برنامه‌های تجاری ABAP | Alchemy Systems SISTEM | Apache Struts | Apple Final Cut Pro | Articulate Rapid E-Learning Studio | Backbone.js | سیستم مدیریت یادگیری Beeline LMS | Blackbaud The Raiser's Edge | نرم‌افزار Blackboard | Blatant Media Absorb LMS | Brainshark Rapid Learning | Cisco Webex | نرم‌افزار رایانش ابری Citrix | Cobent Learning and Compliance Suite LCS | Common Curriculum | سیستم مدیریت یادگیری Computer Generated Solutions | نرم‌افزار پایگاه داده | Django | Drupal | EZ LCMS | Eedo Knowledgeware Eedo Force Ten | ElearningForce JoomlaLMS | Epic Systems | FileMaker Pro | FlexTraining Total e-Learning Solution | G-Cube Solutions Wizdom Web LMS | GeoMetrix Data Systems Training Partner | Google Drive | Google Meet | Google Sites | Google Slides | HP Trim | Halogen eLMS | نرم‌افزار مدیریت منابع انسانی HRMS | زبان نشانه‌گذاری ابرمتن HTML | IBM Notes | IBM SPSS Statistics | ICS Learning Group Inquisiq EX | Ikonami AT-Learning Tool | Inspired eLearning iLMS | Intelladon Enterprise Knowledge Platform EKP | Intelligent Information Conversion Technologies MeritScholar | Intellum Rollbook | Interwoven software | JavaScript | Kahoot! | Learn HQ Activate LMS | سیستم مدیریت یادگیری LMS | LogMeIn GoToMeeting | LogMeIn GoToWebinar | سیستم مدیریت یادگیری Medworxx | Mentimeter | Microsoft Access | Microsoft Dynamics | Microsoft Excel | Microsoft NetMeeting | نرم‌افزار Microsoft Office | Microsoft OneNote | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft SharePoint | Microsoft Visio | Microsoft Word | Moodle | MySQL | Mzinga On-Demand Learning Suite | NetDimensions Enterprise Knowledge Platform EKP | OnPoint Digital OnPoint Learning &amp; Performance Suite | Operitel LearnFlex | Oracle Business Intelligence Enterprise Edition | Oracle PL/SQL | Oracle PeopleSoft | Oracle PeopleSoft Financials | Oracle Solaris | Oracle Taleo | Oracle WebLogic Server | PHP | PRO-ductivity Systems Compliance Training Manager Web | Pathlore LMS | سیستم مدیریت یادگیری Plateau LMS | Poll Everywhere | Prezi | Qarbon ViewletBuilder Professional | RISC Virtual Training Assistant | Right Reason Technologies RightTrack | نرم‌افزار SAP | Screencast-O-Matic | SkillSoft SkillPort | SmugMug Flickr | SumTotal Systems ToolBook | SumTotal Systems TotalLMS | سیستم مدیریت یادگیری Telania eLeaP LMS/LCMS | The Human Equation InSite LMS | TrainCaster LMS | سیستم مدیریت یادگیری TrainOnTrack LMS | Upside Learning UpsideLMS | WeVideo | نرم‌افزار مرورگر وب | Xerceo Learn | سیستم مدیریت محتوای یادگیری Xyleme LCMS | Ziiva Prosperity LMS | Zoom | dominKnow Learning Center | techniques.org knowledgeWorks LMS</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>صحبت کردن | راهبردهای یادگیری | گوش دادن فعال | درک مطلب | نوشتن | تفکر انتقادی | یادگیری فعال | نظارت</t>
+          <t>سخن گفتن | راهبردهای یادگیری | گوش دادن فعال | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -746,17 +746,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شنیداری | درک نوشتاری | بیان نوشتاری | تشخیص گفتار | وضوح گفتار | دید نزدیک | روانی ایده‌ها | حساسیت به مسئله | استدلال قیاسی | خلاقیت | استدلال استقرایی | انعطاف‌پذیری دسته‌بندی | نظم‌دهی اطلاعات | دید دور | توجه انتخابی | حافظه‌سپاری</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | تشخیص گفتار | وضوح گفتار | بینایی نزدیک | روانی ایده‌ها | حساسیت به مسئله | استدلال قیاسی | اصالت | استدلال استقرایی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | بینایی دور | توجه انتخابی | حفظ کردن</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ایمیل | تماس با دیگران | مکالمات تلفنی | بحث‌های حضوری با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | محیط داخلی، دارای کنترل محیطی | صرف زمان برای نشستن | سخنرانی عمومی | فشار زمانی | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | نامه‌ها و یادداشت‌های مکتوب</t>
+          <t>ایمیل | ارتباط با دیگران | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای نشستن | سخنرانی عمومی | فشار زمانی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | نامه‌ها و یادداشت‌های کتبی</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>معلمان آموزش شغلی/فنی، دوره متوسطه | معلمان آموزش شغلی/فنی، پس از متوسطه | معلمان آموزش شغلی/فنی، دوره دبیرستان | مدیران آموزش، مهدکودک تا متوسطه | معلمان آموزش، پس از متوسطه | مدیران آموزش و مراقبت از کودکان، پیش‌دبستانی و مهدکودک | مشاوران و راهنمایان آموزشی، راهنمایی و شغلی | مربیان ورزش و تناسب اندام گروهی | سرپرستان خط اول کارکنان سرگرمی و تفریحی، به جز خدمات قمار | هماهنگ‌کنندگان تناسب اندام و سلامتی | متخصصان آموزش بهداشت | مدیران منابع انسانی | متخصصان منابع انسانی | روان‌شناسان صنعتی-سازمانی | هماهنگ‌کنندگان آموزشی | تحلیل‌گران مدیریت | متخصصان مدیریت پروژه | مشاوران توانبخشی | مدیران آموزش و توسعه | معلمان خصوصی</t>
+          <t>معلمان آموزش‌های شغلی/فنی، دوره راهنمایی | اساتید آموزش‌های شغلی/فنی، پس از متوسطه | معلمان آموزش فنی/حرفه‌ای، دوره متوسطه | مدیران آموزشی، مهدکودک تا دبیرستان | مدرسان علوم تربیتی، آموزش عالی | مدیران آموزش و مراقبت از کودکان، پیش‌دبستانی و مهدکودک | مشاوران و راهنمایان آموزشی، شغلی و تحصیلی | مربیان ورزشی و مدرسان تناسب اندام گروهی | سرپرستان خط اول کارگران سرگرمی و تفریح، به جز خدمات قمار | هماهنگ‌کنندگان تناسب اندام و سلامتی | متخصصان آموزش بهداشت | مدیران منابع انسانی | متخصصان منابع انسانی | روان‌شناسان صنعتی-سازمانی | هماهنگ‌کنندگان آموزشی | تحلیل‌گران مدیریت | متخصصان مدیریت پروژه | مشاوران توانبخشی | مدیران آموزش و توسعه | معلمان خصوصی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -788,32 +788,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3M Post-it App | AcaStat Software | Act! | نرم‌افزار تحلیل مشترک تطبیقی ACA | Adobe Acrobat | Adobe ActionScript | Adobe After Effects | نرم‌افزار Adobe Creative Cloud | Adobe Dreamweaver | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Adxstudio, for Microsoft | Airtable | Amazon Redshift | AndersonBell Abstat | Apache Hadoop | Apache Hive | Apache Pig | Apple Final Cut Pro | Apple Keynote | Apple macOS | Aprimo Marketing | Asana | Basecamp | Blackbaud The Raiser's Edge | Canva | Cascading style sheets CSS | ClassApps SelectSurveyASP | Cytel LogXact | Cytel Software XLMiner | نرم‌افزار تحلیل داده | نرم‌افزار پایگاه داده | Delphi Technology | نرم‌افزار Digivey (ویژگی سیستم خبره) | نرم‌افزار Digivey (ویژگی نقطه فروش) | Dropbox | Drupal | Dynamic hypertext markup language DHTML | ESRI ArcGIS software | Evernote | Extensible hypertext markup language XHTML | Facebook | Factiva | FedBizOps | FileMaker Pro | نرم‌افزار برنامه‌ریزی مالی | GLOBE Claritas | GMI NET-MR | Galilee Enterprise TargetPro | نرم‌افزار بازاریابی سیستم اطلاعات جغرافیایی GIS | Google Ads | Google Analytics | Google Docs | Google Drive | Google Looker Analytics | Google Slides | GroupMe | نرم‌افزار HubSpot | Hypertext markup language HTML | IBM Cognos Impromptu | IBM Information Management System (IMS) | IBM Intelligent Miner | IBM Notes | IBM SPSS Statistics | Insightful Corporation Confirmit | Insightful S-PLUS | Instagram | Intellimed | JavaScript | LexisNexis | LinkedIn | LogMeIn GoToMeeting | LogMeIn GoToWebinar | LogiXML Ad-HOC | Loom | Map Maker | Marketo Marketing Automation | Medstat/INFORUM | MicroStrategy | Microsoft Access | Microsoft Dynamics | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft SQL Server | Microsoft SharePoint | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic for Applications VBA | Microsoft Word | Minitab | Mintel Reports | MySQL | NCR Teradata Warehouse Miner | Neoforma Healthcare Products Information Services HPIS Market Intelligence | NetSuite ERP | NortonLifeLock cybersecurity software | Oracle Business Intelligence Enterprise Edition | Oracle Darwin | Oracle Eloqua | Oracle Hyperion | Oracle PeopleSoft | PHP | Palisade StatTools | Perseus SurveySolutions | Provalis Research Simstat | Qlik Tech QlikView | R | Red Hat Enterprise Linux | SAP Business Objects | SAP Crystal Reports | نرم‌افزار SAP | SAS | نرم‌افزار Salesforce | Sawtooth Choice-Base Conjoint CBS | Sawtooth Composite Product Mapping CPM | Sawtooth SSI Web | Slack | SmugMug Flickr | سایت‌های رسانه‌های اجتماعی | StatPac | StataCorp Stata | Structured query language SQL | نرم‌افزار نظرسنجی | TNS MarketWhys | TNS Miriad | Tableau | TechExcel ServiceWise | Teradata Database | The MathWorks MATLAB | Thomson Dialog | Thomson Financial Investext | TikTok | TranspoLink BidLeads | UNISTAT Statistical Package | Vantage MCIF | Verispan Patient Parameters | Walmart Retail Link | WeVideo | نرم‌افزار مرورگر وب | WinCross | WordPress | WorldAPP KeySurvey Suite | YouTube | Zoom</t>
+          <t>3M Post-it App | AcaStat Software | Act! | نرم‌افزار تحلیل مشترک تطبیقی ACA | Adobe Acrobat | Adobe ActionScript | Adobe After Effects | نرم‌افزار Adobe Creative Cloud | Adobe Dreamweaver | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Adxstudio, for Microsoft | Airtable | Amazon Redshift | AndersonBell Abstat | Apache Hadoop | Apache Hive | Apache Pig | Apple Final Cut Pro | Apple Keynote | Apple macOS | Aprimo Marketing | Asana | Basecamp | Blackbaud The Raiser's Edge | Canva | برگه‌های سبک آبشاری CSS | ClassApps SelectSurveyASP | Cytel LogXact | Cytel Software XLMiner | نرم‌افزار تحلیل داده | نرم‌افزار پایگاه داده | Delphi Technology | نرم‌افزار Digivey (ویژگی سیستم خبره) | نرم‌افزار Digivey (ویژگی نقطه فروش) | Dropbox | Drupal | زبان نشانه‌گذاری ابرمتن پویا DHTML | نرم‌افزار ESRI ArcGIS | Evernote | زبان نشانه‌گذاری ابرمتن توسعه‌پذیر XHTML | Facebook | Factiva | FedBizOps | FileMaker Pro | نرم‌افزار برنامه‌ریزی مالی | GLOBE Claritas | GMI NET-MR | Galilee Enterprise TargetPro | نرم‌افزار بازاریابی سیستم اطلاعات جغرافیایی GIS | Google Ads | Google Analytics | Google Docs | Google Drive | Google Looker Analytics | Google Slides | GroupMe | نرم‌افزار HubSpot | زبان نشانه‌گذاری ابرمتن HTML | IBM Cognos Impromptu | IBM Information Management System (IMS) | IBM Intelligent Miner | IBM Notes | IBM SPSS Statistics | Insightful Corporation Confirmit | Insightful S-PLUS | Instagram | Intellimed | JavaScript | LexisNexis | LinkedIn | LogMeIn GoToMeeting | LogMeIn GoToWebinar | LogiXML Ad-HOC | Loom | Map Maker | Marketo Marketing Automation | Medstat/INFORUM | MicroStrategy | Microsoft Access | Microsoft Dynamics | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft SQL Server | Microsoft SharePoint | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic for Applications VBA | Microsoft Word | Minitab | Mintel Reports | MySQL | NCR Teradata Warehouse Miner | Neoforma Healthcare Products Information Services HPIS Market Intelligence | NetSuite ERP | نرم‌افزار امنیت سایبری NortonLifeLock | Oracle Business Intelligence Enterprise Edition | Oracle Darwin | Oracle Eloqua | Oracle Hyperion | Oracle PeopleSoft | PHP | Palisade StatTools | Perseus SurveySolutions | Provalis Research Simstat | Qlik Tech QlikView | R | Red Hat Enterprise Linux | SAP Business Objects | SAP Crystal Reports | نرم‌افزار SAP | SAS | نرم‌افزار Salesforce | Sawtooth Choice-Base Conjoint CBS | Sawtooth Composite Product Mapping CPM | Sawtooth SSI Web | Slack | SmugMug Flickr | سایت‌های رسانه‌های اجتماعی | StatPac | StataCorp Stata | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار نظرسنجی | TNS MarketWhys | TNS Miriad | Tableau | TechExcel ServiceWise | Teradata Database | The MathWorks MATLAB | Thomson Dialog | Thomson Financial Investext | TikTok | TranspoLink BidLeads | UNISTAT Statistical Package | Vantage MCIF | Verispan Patient Parameters | Walmart Retail Link | WeVideo | نرم‌افزار مرورگر وب | WinCross | WordPress | WorldAPP KeySurvey Suite | YouTube | Zoom</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نوشتن | درک مطلب | گوش دادن فعال | صحبت کردن | یادگیری فعال | نظارت | ریاضیات | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | نگارش | درک مطلب | گوش دادن فعال | سخن گفتن | یادگیری فعال | نظارت | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | خدمات مشتری و شخصی | فروش و بازاریابی | ریاضیات | مدیریت و اداره | ارتباطات و رسانه | اداری | رایانه و الکترونیک | جامعه‌شناسی و مردم‌شناسی | روان‌شناسی | اقتصاد و حسابداری</t>
+          <t>زبان انگلیسی | خدمات مشتری و شخصی | فروش و بازاریابی | ریاضیات | مدیریت و اداره | ارتباطات و رسانه | اداری | رایانه و الکترونیک | جامعه‌شناسی و انسان‌شناسی | روان‌شناسی | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>استدلال استقرایی | درک نوشتاری | بیان شفاهی | بیان نوشتاری | روانی ایده‌ها | استدلال قیاسی | درک شنیداری | نظم‌دهی اطلاعات | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | دید نزدیک | حساسیت به مسئله | استدلال ریاضی | خلاقیت | تشخیص گفتار | تسهیلات عددی | انعطاف‌پذیری بستار</t>
+          <t>استدلال استقرایی | درک کتبی | بیان شفاهی | بیان کتبی | روانی ایده‌ها | استدلال قیاسی | درک شفاهی | ترتیب‌دهی اطلاعات | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | حساسیت به مسئله | استدلال ریاضی | اصالت | تشخیص گفتار | توانایی عددی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ایمیل | صرف زمان برای نشستن | مکالمات تلفنی | آزادی در تصمیم‌گیری | اهمیت دقیق یا صحیح بودن | تعیین وظایف، اولویت‌ها و اهداف | تماس با دیگران | بحث‌های حضوری با افراد و درون تیم‌ها | فشار زمانی | محیط داخلی، دارای کنترل محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | نامه‌ها و یادداشت‌های مکتوب | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری</t>
+          <t>ایمیل | صرف زمان برای نشستن | مکالمات تلفنی | آزادی در تصمیم‌گیری | اهمیت دقیق یا درست بودن | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فشار زمانی | محیط داخلی، دارای کنترل شرایط محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | نامه‌ها و یادداشت‌های کتبی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>نمایندگان فروش تبلیغات | مدیران تبلیغات و ترویج | تحلیل‌گران هوش تجاری | مدرسان کسب‌وکار، پس از متوسطه | دانشمندان داده | متخصصان ریسک مالی | تحلیل‌گران مالی و سرمایه‌گذاری | تحلیل‌گران مدیریت | مدیران بازاریابی | تجار آنلاین | مشاوران مالی شخصی | مدیران روابط عمومی | متخصصان روابط عمومی | مدیران فروش | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و مسافرتی | استراتژیست‌های بازاریابی جستجو | نمایندگان فروش اوراق بهادار، کالا و خدمات مالی | محققان نظرسنجی | خریداران عمده و خرده‌فروشی، به جز محصولات کشاورزی | نویسندگان و مؤلفان</t>
+          <t>نمایندگان فروش تبلیغات | مدیران تبلیغات و ترویج | تحلیلگران هوش تجاری | اساتید کسب‌وکار، پس از متوسطه | دانشمندان داده | متخصصان ریسک مالی | تحلیلگران مالی و سرمایه‌گذاری | تحلیل‌گران مدیریت | مدیران بازاریابی | تاجران آنلاین | مشاوران مالی شخصی | مدیران روابط عمومی | متخصصان روابط عمومی | مدیران فروش | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | استراتژیست‌های بازاریابی جستجو | نمایندگان فروش اوراق بهادار، کالاها و خدمات مالی | پژوهشگران نظرسنجی | خریداران عمده‌فروشی و خرده‌فروشی، به جز محصولات کشاورزی | نویسندگان و مؤلفان</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -845,12 +845,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>AJAX | Adobe Analytics | Adobe Dreamweaver | Adobe Photoshop | Ahrefs Site Explorer | Apache Solr | Atlas Search | Bing Ads | BrightEdge | Cascading style sheets CSS | Conductor Searchlight | سیستم‌های مدیریت محتوا CMS | پایگاه‌های داده اطلاعات مشتری | Drupal | Elasticsearch | نرم‌افزار ایمیل | Facebook | Google | Google Ads | Google Analytics | Google Looker Analytics | Google Search Ads 360 | Google Tag Manager | Google Webmaster Tools | نرم‌افزار HubSpot | Hypertext markup language HTML | IBM Digital Analytics | JamBoard | JavaScript | Kanoodle | LinkedIn | Majestic SEO | Marketo Marketing Automation | Microsoft ASP.NET | Microsoft Access | Microsoft Bing | Microsoft Dynamics | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft Visio | Microsoft Word | نرم‌افزار بهینه‌سازی موتور جستجو Moz SEO | MySQL | پایگاه‌های داده آنلاین | Open Source Matters Joomla! | Oracle Eloqua | Oracle Java | Oracle JavaServer Pages JSP | PHP | Pinterest | Python | Screaming Frog SEO Spider | Searchmetrics Suite | Semrush | Structured query language SQL | Tableau | Twitter | نرم‌افزار مرورگر وب | WhatsApp | WordPress | Yahoo! Email | YouTube | seoClarity</t>
+          <t>AJAX | Adobe Analytics | Adobe Dreamweaver | Adobe Photoshop | Ahrefs Site Explorer | Apache Solr | Atlas Search | Bing Ads | BrightEdge | برگه‌های سبک آبشاری CSS | Conductor Searchlight | سیستم‌های مدیریت محتوا CMS | پایگاه‌های داده اطلاعات مشتریان | Drupal | Elasticsearch | نرم‌افزار ایمیل | Facebook | Google | Google Ads | Google Analytics | Google Looker Analytics | Google Search Ads 360 | Google Tag Manager | Google Webmaster Tools | نرم‌افزار HubSpot | زبان نشانه‌گذاری ابرمتن HTML | IBM Digital Analytics | JamBoard | JavaScript | Kanoodle | LinkedIn | Majestic SEO | Marketo Marketing Automation | Microsoft ASP.NET | Microsoft Access | Microsoft Bing | Microsoft Dynamics | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft Visio | Microsoft Word | نرم‌افزار بهینه‌سازی موتور جستجو Moz SEO | MySQL | پایگاه‌های داده آنلاین | Open Source Matters Joomla! | Oracle Eloqua | Oracle Java | Oracle JavaServer Pages JSP | PHP | Pinterest | Python | Screaming Frog SEO Spider | Searchmetrics Suite | Semrush | زبان پرس‌وجوی ساختاریافته SQL | Tableau | Twitter | نرم‌افزار مرورگر وب | WhatsApp | WordPress | Yahoo! Email | YouTube | seoClarity</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | یادگیری فعال | گوش دادن فعال | تفکر انتقادی | صحبت کردن | نوشتن | نظارت</t>
+          <t>درک مطلب | یادگیری فعال | گوش دادن فعال | تفکر انتقادی | سخن گفتن | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -860,17 +860,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شنیداری | درک نوشتاری | بیان شفاهی | بیان نوشتاری | روانی ایده‌ها | حساسیت به مسئله | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | نظم‌دهی اطلاعات | استدلال استقرایی | انعطاف‌پذیری دسته‌بندی | خلاقیت | دید نزدیک | انعطاف‌پذیری بستار | توجه انتخابی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | روانی ایده‌ها | حساسیت به مسئله | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | ترتیب‌دهی اطلاعات | استدلال استقرایی | انعطاف‌پذیری دسته‌بندی | اصالت | بینایی نزدیک | انعطاف‌پذیری بستار | توجه انتخابی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>ایمیل | صرف زمان برای نشستن | آزادی در تصمیم‌گیری | محیط داخلی، دارای کنترل محیطی | مکالمات تلفنی | تعیین وظایف، اولویت‌ها و اهداف | بحث‌های حضوری با افراد و درون تیم‌ها | اهمیت دقیق یا صحیح بودن | فشار زمانی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | کار با یا مشارکت در یک گروه کاری یا تیم | تماس با دیگران | سطح رقابت</t>
+          <t>ایمیل | صرف زمان برای نشستن | آزادی در تصمیم‌گیری | محیط داخلی، دارای کنترل شرایط محیطی | مکالمات تلفنی | تعیین وظایف، اولویت‌ها و اهداف | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | فشار زمانی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | سطح رقابت</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>نمایندگان فروش تبلیغات | مدیران تبلیغات و ترویج | تحلیل‌گران هوش تجاری | برنامه‌نویسان رایانه | تحلیل‌گران سیستم‌های رایانه‌ای | دانشمندان داده | متخصصان مدیریت اسناد | تحلیل‌گران مدیریت | تحلیل‌گران تحقیقات بازار و متخصصان بازاریابی | مدیران بازاریابی | تجار آنلاین | مدیران روابط عمومی | متخصصان روابط عمومی | مدیران فروش | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و مسافرتی | توسعه‌دهندگان نرم‌افزار | مدیران وب | توسعه‌دهندگان وب | طراحان وب و رابط دیجیتال | نویسندگان و مؤلفان</t>
+          <t>نمایندگان فروش تبلیغات | مدیران تبلیغات و ترویج | تحلیلگران هوش تجاری | برنامه‌نویسان کامپیوتر | تحلیلگران سیستم‌های کامپیوتری | دانشمندان داده | متخصصان مدیریت اسناد | تحلیل‌گران مدیریت | تحلیل‌گران تحقیقات بازار و متخصصان بازاریابی | مدیران بازاریابی | تاجران آنلاین | مدیران روابط عمومی | متخصصان روابط عمومی | مدیران فروش | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | توسعه‌دهندگان نرم‌افزار | مدیران وب | توسعه‌دهندگان وب | طراحان رابط دیجیتال و وب | نویسندگان و مؤلفان</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -902,12 +902,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Microsoft Excel | Microsoft Word | Microsoft PowerPoint | Microsoft Outlook | نرم‌افزار Microsoft Office | نرم‌افزار ایمیل | Microsoft Access | Microsoft SharePoint | نرم‌افزار مرورگر وب | نرم‌افزار پایگاه داده | Google Docs | نرم‌افزار مدیریت تقویم | برنامه‌های صفحه‌گسترده | Adobe Acrobat | Microsoft Project | Microsoft Power BI | Tableau | Structured query language SQL | سیستم برنامه‌ریزی منابع سازمانی ERP</t>
+          <t>Microsoft Excel | Microsoft Word | Microsoft PowerPoint | Microsoft Outlook | نرم‌افزار Microsoft Office | نرم‌افزار ایمیل | Microsoft Access | Microsoft SharePoint | نرم‌افزار مرورگر وب | نرم‌افزار پایگاه داده | Google Docs | نرم‌افزار مدیریت تقویم | برنامه‌های صفحه‌گسترده | Adobe Acrobat | Microsoft Project | Microsoft Power BI | Tableau | زبان پرس‌وجوی ساختاریافته SQL | سیستم برنامه‌ریزی منابع سازمانی ERP</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | صحبت کردن | نوشتن | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -917,17 +917,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شنیداری | درک نوشتاری | بیان شفاهی | بیان نوشتاری | استدلال قیاسی | استدلال استقرایی | نظم‌دهی اطلاعات | حساسیت به مسئله | دید نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | خلاقیت | توجه انتخابی | اشتراک زمانی | تجسم | حافظه‌سپاری | استدلال ریاضی | تسهیلات عددی | سرعت ادراکی | انعطاف‌پذیری بستار</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن | استدلال ریاضی | توانایی عددی | سرعت ادراکی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | بحث‌های حضوری با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل محیطی | صرف زمان برای نشستن | تماس با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا صحیح بودن | فشار زمانی | نامه‌ها و یادداشت‌های مکتوب | تناوب تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | سطح رقابت</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای نشستن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | سطح رقابت</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>تحلیل‌گران مدیریت | متخصصان مدیریت پروژه | برنامه‌ریزان تداوم کسب‌وکار | متخصصان پایداری | متخصصان مدیریت امنیت | تجار آنلاین | تدارکات‌چی‌ها | تحلیل‌گران تدارکات | افسران انطباق | برآوردکنندگان هزینه | متخصصان منابع انسانی | متخصصان آموزش و توسعه | برنامه‌ریزان جلسات، همایش‌ها و رویدادها | تحلیل‌گران تحقیقات بازار و متخصصان بازاریابی | جمع‌آوری‌کنندگان کمک مالی | متخصصان روابط کار | متخصصان جبران خدمات، مزایا و تحلیل شغل | نمایندگان خرید، به جز عمده‌فروشی، خرده‌فروشی و محصولات کشاورزی | مدیران عمومی و عملیات | حسابداران و حسابرسان</t>
+          <t>تحلیل‌گران مدیریت | متخصصان مدیریت پروژه | برنامه‌ریزان تداوم کسب‌وکار | متخصصان پایداری | متخصصان مدیریت امنیت | تاجران آنلاین | لجستیسین‌ها | تحلیلگران لجستیک | افسران انطباق | برآوردکنندگان هزینه | متخصصان منابع انسانی | متخصصان آموزش و توسعه | برنامه‌ریزان جلسات، همایش‌ها و رویدادها | تحلیل‌گران تحقیقات بازار و متخصصان بازاریابی | جمع‌آوری‌کنندگان کمک مالی | متخصصان روابط کار | متخصصان جبران خدمات، مزایا و تحلیل شغل | نمایندگان خرید، به جز عمده‌فروشی، خرده‌فروشی و محصولات کشاورزی | مدیران عمومی و عملیات | حسابداران و حسابرسان</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -959,12 +959,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Actuate BIRT | Adobe Acrobat | Atlassian Confluence | Atlassian JIRA | نرم‌افزار تداوم کسب‌وکار | CA Clarity PPM | COOP Systems myCOOP | سیستم‌های عامل رایانه | EMC RSA Archer Business Continuity Management | نرم‌افزار سیستم اطلاع‌رسانی اضطراری | سیستم‌های پشتیبان‌گیری سازمانی | Jaspersoft Business Intelligence Suite | نرم‌افزار شبکه محلی LAN | MIR3 Intelligent Notification | Mentimeter | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft SharePoint | Microsoft SharePoint Server | Microsoft Visio | Microsoft Word | Oracle JD Edwards EnterpriseOne | Oracle Primavera Enterprise Project Portfolio Management | RecoveryPlanner RPX | SAP Crystal Reports | ServiceNow | Strategic BCP ResilienceONE | Structured query language SQL | SunGard NotiFind | Sungard Assurance | Teradata Database | Virtual Corporation Sustainable Planner | نرم‌افزار مرورگر وب</t>
+          <t>Actuate BIRT | Adobe Acrobat | Atlassian Confluence | Atlassian JIRA | نرم‌افزار تداوم کسب‌وکار | CA Clarity PPM | COOP Systems myCOOP | سیستم‌های عامل رایانه | EMC RSA Archer Business Continuity Management | نرم‌افزار سیستم اطلاع‌رسانی اضطراری | سیستم‌های پشتیبان‌گیری سازمانی | Jaspersoft Business Intelligence Suite | نرم‌افزار شبکه محلی LAN | MIR3 Intelligent Notification | Mentimeter | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft SharePoint | Microsoft SharePoint Server | Microsoft Visio | Microsoft Word | Oracle JD Edwards EnterpriseOne | Oracle Primavera Enterprise Project Portfolio Management | RecoveryPlanner RPX | SAP Crystal Reports | ServiceNow | Strategic BCP ResilienceONE | زبان پرس‌وجوی ساختاریافته SQL | SunGard NotiFind | Sungard Assurance | Teradata Database | Virtual Corporation Sustainable Planner | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | تفکر انتقادی | درک مطلب | یادگیری فعال | صحبت کردن | نوشتن | نظارت | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | تفکر انتقادی | درک مطلب | یادگیری فعال | سخن گفتن | نگارش | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -974,17 +974,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | استدلال استقرایی | درک شنیداری | درک نوشتاری | بیان شفاهی | بیان نوشتاری | استدلال قیاسی | نظم‌دهی اطلاعات | روانی ایده‌ها | تشخیص گفتار | وضوح گفتار | دید نزدیک | خلاقیت | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | توجه انتخابی</t>
+          <t>حساسیت به مسئله | استدلال استقرایی | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | ترتیب‌دهی اطلاعات | روانی ایده‌ها | تشخیص گفتار | وضوح گفتار | بینایی نزدیک | اصالت | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | صرف زمان برای نشستن | کار با یا مشارکت در یک گروه کاری یا تیم | تماس با دیگران | محیط داخلی، دارای کنترل محیطی | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | تعیین وظایف، اولویت‌ها و اهداف | بحث‌های حضوری با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا صحیح بودن</t>
+          <t>ایمیل | مکالمات تلفنی | صرف زمان برای نشستن | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | محیط داخلی، دارای کنترل شرایط محیطی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تعیین وظایف، اولویت‌ها و اهداف | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا درست بودن</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری | تحلیل‌گران هوش تجاری | مدیران ارشد پایداری | مدیران انطباق | تحلیل‌گران سیستم‌های رایانه‌ای | مهندسان/معماران سیستم‌های رایانه‌ای | مدیران سیستم‌های رایانه‌ای و اطلاعاتی | مدیران پایگاه داده | متخصصان مدیریت اسناد | مدیران مدیریت اضطراری | متخصصان ریسک مالی | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | مدیران پروژه فناوری اطلاعات | تدارکات‌چی‌ها | تحلیل‌گران تدارکات | تحلیل‌گران مدیریت | متخصصان مدیریت پروژه | متخصصان مدیریت امنیت | مدیران امنیت</t>
+          <t>مدیران خدمات اداری | تحلیلگران هوش تجاری | مدیران ارشد پایداری | مدیران انطباق | تحلیلگران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | مدیران کامپیوتر و سیستم‌های اطلاعاتی | مدیران پایگاه داده | متخصصان مدیریت اسناد | مدیران مدیریت بحران | متخصصان ریسک مالی | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | مدیران پروژه فناوری اطلاعات | لجستیسین‌ها | تحلیلگران لجستیک | تحلیل‌گران مدیریت | متخصصان مدیریت پروژه | متخصصان مدیریت امنیت | مدیران امنیتی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1016,12 +1016,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Adobe Acrobat | نرم‌افزار Adobe Creative Cloud | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Autodesk AutoCAD | Autodesk AutoCAD Civil 3D | Autodesk Revit | Bentley MicroStation | Esri ArcGIS | Extensible markup language XML | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | Google Analytics | سیستم‌های مدیریت موجودی | JavaScript | نرم‌افزار ارزیابی چرخه عمر LCA | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Power BI | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft SharePoint | Microsoft Visio | Microsoft Word | نرم‌افزار جستجو و بازیابی پایگاه داده آنلاین | Oracle Database | PE INTERNATIONAL GaBi | PE INTERNATIONAL SoFi | PRe Consultants SimaPro | نرم‌افزار نشر سازمانی Quark | نرم‌افزار SAP | سایت‌های رسانه‌های اجتماعی | Structured query language SQL | Tableau | نرم‌افزار مرورگر وب</t>
+          <t>Adobe Acrobat | نرم‌افزار Adobe Creative Cloud | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Autodesk AutoCAD | Autodesk AutoCAD Civil 3D | Autodesk Revit | Bentley MicroStation | Esri ArcGIS | زبان نشانه‌گذاری توسعه‌پذیر XML | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | Google Analytics | سیستم‌های مدیریت موجودی | JavaScript | نرم‌افزار ارزیابی چرخه عمر LCA | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Power BI | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft SharePoint | Microsoft Visio | Microsoft Word | نرم‌افزار جستجو و بازیابی پایگاه داده آنلاین | Oracle Database | PE INTERNATIONAL GaBi | PE INTERNATIONAL SoFi | PRe Consultants SimaPro | نرم‌افزار نشر سازمانی Quark | نرم‌افزار SAP | سایت‌های رسانه‌های اجتماعی | زبان پرس‌وجوی ساختاریافته SQL | Tableau | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>صحبت کردن | نوشتن | درک مطلب | گوش دادن فعال | تفکر انتقادی | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>سخن گفتن | نگارش | درک مطلب | گوش دادن فعال | تفکر انتقادی | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1031,17 +1031,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک نوشتاری | بیان نوشتاری | درک شنیداری | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | حساسیت به مسئله | نظم‌دهی اطلاعات | خلاقیت | تشخیص گفتار | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | دید نزدیک | استدلال ریاضی</t>
+          <t>درک کتبی | بیان کتبی | درک شفاهی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | حساسیت به مسئله | ترتیب‌دهی اطلاعات | اصالت | تشخیص گفتار | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | بحث‌های حضوری با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | تماس با دیگران | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای نشستن | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | محیط داخلی، دارای کنترل محیطی | آزادی در تصمیم‌گیری | فشار زمانی | اهمیت دقیق یا صحیح بودن | نامه‌ها و یادداشت‌های مکتوب</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای نشستن | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | محیط داخلی، دارای کنترل شرایط محیطی | آزادی در تصمیم‌گیری | فشار زمانی | اهمیت دقیق یا درست بودن | نامه‌ها و یادداشت‌های کتبی</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>مدیران معماری و مهندسی | مدیران توسعه فناوری و محصول سوخت‌های زیستی/بیودیزل | متخصصان بازسازی زمین‌های قهوه‌ای و مدیران سایت | مدیران ارشد پایداری | تحلیل‌گران سیاست تغییر اقلیم | دانشمندان حفاظت | ممیزان انرژی | مهندسان انرژی، به جز باد و خورشیدی | مهندسان محیط زیست | برنامه‌ریزان احیای محیط زیست | دانشمندان و متخصصان محیط زیست، از جمله بهداشت | بوم‌شناسان صنعتی | مدیران پروژه فناوری اطلاعات | معماران منظر | تحلیل‌گران مدیریت | متخصصان مدیریت پروژه | نمایندگان فروش و ارزیابان خورشیدی | برنامه‌ریزان شهری و منطقه‌ای | متخصصان منابع آب | مدیران توسعه انرژی باد</t>
+          <t>مدیران معماری و مهندسی | مدیران توسعه محصول و فناوری سوخت‌های زیستی/بیودیزل | متخصصان بازآفرینی زمین‌های قهوه‌ای و مدیران سایت | مدیران ارشد پایداری | تحلیل‌گران سیاست تغییرات اقلیمی | دانشمندان حفاظت | بازرسان انرژی | مهندسان انرژی، به جز باد و خورشید | مهندسان محیط زیست | برنامه‌ریزان احیای محیط‌زیست | دانشمندان و متخصصان محیط زیست، شامل بهداشت | بوم‌شناسان صنعتی | مدیران پروژه فناوری اطلاعات | معماران منظر | تحلیل‌گران مدیریت | متخصصان مدیریت پروژه | نمایندگان و ارزیابان فروش تجهیزات خورشیدی | برنامه‌ریزان شهری و منطقه‌ای | متخصصان منابع آب | مدیران توسعه انرژی بادی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0009_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0009_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | تفکر انتقادی | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری | ریاضیات</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | مدیریت و امور اداری | خدمات مشتریان و خدمات فردی | ریاضیات | آموزش و تدریس | رایانه و الکترونیک | اقتصاد و حسابداری | امور کارکنان و منابع انسانی | حقوق و مقررات دولتی | فروش و بازاریابی | روان‌شناسی | ارتباطات و رسانه | جامعه‌شناسی و مردم‌شناسی</t>
+          <t>زبان انگلیسی | مدیریت و اداره | خدمات مشتری و شخصی | ریاضیات | آموزش و پرورش | رایانه و الکترونیک | اقتصاد و حسابداری | پرسنل و منابع انسانی | قانون و دولت | فروش و بازاریابی | روان‌شناسی | ارتباطات و رسانه | جامعه‌شناسی و انسان‌شناسی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | بیان کتبی | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | روانی کلام و ایده‌پردازی | مرتب‌سازی اطلاعات | دید نزدیک | انعطاف‌پذیری در دسته‌بندی | ابتکار و اصالت | توجه انتخابی | انعطاف‌پذیری در ادراک الگوها | استدلال ریاضی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | بیان کتبی | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | روانی ایده‌ها | ترتیب‌دهی اطلاعات | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | اصالت | توجه انتخابی | انعطاف‌پذیری بستار | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری | کارشناسان برنامه‌ریزی تداوم کسب‌وکار | کارشناسان تحلیل هوش تجاری | مدرسان علوم بازرگانی و اداری، آموزش عالی | مدیران ارشد اجرایی | مدیران انطباق و نظارت قانونی | کارشناسان تحلیل سیستم‌های کامپیوتری | مدیران فناوری اطلاعات و سیستم‌های کامپیوتری | دانشمندان علم داده | متخصصان مدیریت اسناد و مدارک | کارشناسان تحلیل ریسک مالی | سرپرستان رده‌اول کارکنان پشتیبانی دفتری و اداری | کارشناسان فناوری اطلاعات سلامت و ثبت آمار پزشکی | روان‌شناسان صنعتی و سازمانی | مدیران پروژه‌های فناوری اطلاعات | کارشناسان تحلیل تحقیقات بازار و بازاریابی | کارشناسان تحلیل تحقیق در عملیات | متخصصان مدیریت پروژه | دستیاران آمار | مدیران آموزش و بهسازی منابع انسانی</t>
+          <t>مدیران خدمات اداری و پشتیبانی | کارشناسان برنامه‌ریزی تداوم کسب‌وکار | تحلیل‌گران هوش تجاری | استادان علوم اداری و مدیریت، آموزش عالی | مدیران عامل و مدیران ارشد اجرایی | مدیران تطبیق و نظارت مقرراتی | تحلیل‌گران سیستم‌های کامپیوتری | مدیران فناوری اطلاعات و سیستم‌های رایانه‌ای | دانشمندان داده | کارشناسان مدیریت اسناد و مدارک | کارشناسان ریسک مالی | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | کارشناسان فناوری اطلاعات سلامت و ثبت داده‌های پزشکی | روان‌شناسان صنعتی و سازمانی | مدیران پروژه‌های فناوری اطلاعات | کارشناسان تحلیل تحقیقات بازار و بازاریابی | تحلیل‌گران تحقیق در عملیات | کارشناسان مدیریت پروژه | دستیاران و تکنسین‌های آمار | مدیران آموزش و بهسازی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب | سخن گفتن | تفکر انتقادی | نگارش | نظارت | یادگیری فعال</t>
+          <t>گوش دادن فعال | درک مطلب | سخن گفتن | تفکر انتقادی | نگارش | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | ارتباطات و رسانه | امور اداری و دفتری | مدیریت و امور اداری | رایانه و الکترونیک | ایمنی و امنیت عمومی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | ارتباطات و رسانه | اداری | مدیریت و اداره | رایانه و الکترونیک | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | تشخیص گفتار | حساسیت به مسئله | استدلال قیاسی | وضوح گفتار | روانی کلام و ایده‌پردازی | دید نزدیک | ابتکار و اصالت | استدلال استقرایی | مرتب‌سازی اطلاعات | انعطاف‌پذیری در دسته‌بندی | دید دور | توجه انتخابی | اشتراک زمانی | تجسم فضایی | استدلال ریاضی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | تشخیص گفتار | حساسیت به مسئله | استدلال قیاسی | وضوح گفتار | روانی ایده‌ها | بینایی نزدیک | اصالت | استدلال استقرایی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | بینایی دور | توجه انتخابی | تقسیم توجه | تجسم | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری | مدیران برنامه‌ها و کارگزاران هنرمندان، مجریان و ورزشکاران | کارشناسان برنامه‌ریزی تداوم کسب‌وکار | مسئولان دفاتر و دستیاران اجرایی مدیریت | سرپرستان رده‌اول کارکنان حوزه تفریحات و سرگرمی، به‌جز خدمات شرط‌بندی | سرپرستان رده‌اول فروشندگان خدمات و کالاهای غیرخرده‌فروشی | سرپرستان رده‌اول کارکنان پشتیبانی دفتری و اداری | کارشناسان جذب منابع مالی و حامی | مدیران جذب منابع مالی | مدیران پروژه‌های فناوری اطلاعات | کارشناسان لجستیک و زنجیره تأمین | کارشناسان تحلیل مدیریت و روش‌ها | مدیران برنامه‌ریزی رسانه‌ای | متخصصان مدیریت پروژه | مدیران روابط عمومی | کارشناسان روابط عمومی | کارشناسان امور تفریحی و اوقات فراغت | کارشناسان فروش خدمات، به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری | مسئولان امور دفتری و کارشناسان امور اداری | مدیران خدمات اجتماعی و عام‌المنفعه</t>
+          <t>مدیران خدمات اداری و پشتیبانی | مدیران برنامه‌ها و نمایندگان هنرمندان، مجریان و ورزشکاران | کارشناسان برنامه‌ریزی تداوم کسب‌وکار | مسئولان دفاتر و دستیاران اجرایی مدیریت | سرپرستان رده‌اول کارکنان مراکز تفریحی و سرگرمی، به‌جز بازی‌های شرط‌بندی | سرپرستان رده‌اول فروشندگان عمده‌فروشی و غیرخرده‌فروشی | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | کارشناسان جذب منابع مالی و حامی | مدیران جذب منابع مالی و حامیان | مدیران پروژه‌های فناوری اطلاعات | کارشناسان لجستیک و مدیریت زنجیره تأمین | کارشناسان تحلیل مدیریت و روش‌ها | مدیران برنامه‌ریزی و پخش رسانه | کارشناسان مدیریت پروژه | مدیران روابط عمومی | کارشناسان روابط عمومی | کارکنان و متصدیان امور تفریحی و اوقات فراغت | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری) | منشی‌ها و دستیاران اداری عمومی | مدیران خدمات اجتماعی و خدمات مردمی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>سخن گفتن | نگارش | شنیدن فعال | درک مطلب | تفکر انتقادی | یادگیری فعال | نظارت | ریاضیات</t>
+          <t>سخن گفتن | نگارش | گوش دادن فعال | درک مطلب | تفکر انتقادی | یادگیری فعال | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | فروش و بازاریابی | مدیریت و امور اداری | ارتباطات و رسانه | اقتصاد و حسابداری | رایانه و الکترونیک | امور اداری و دفتری</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | فروش و بازاریابی | مدیریت و اداره | ارتباطات و رسانه | اقتصاد و حسابداری | رایانه و الکترونیک | اداری</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>بیان شفاهی | وضوح گفتار | درک شفاهی | درک کتبی | بیان کتبی | تشخیص گفتار | استدلال استقرایی | استدلال قیاسی | روانی کلام و ایده‌پردازی | دید نزدیک | حساسیت به مسئله | مرتب‌سازی اطلاعات | ابتکار و اصالت | انعطاف‌پذیری در دسته‌بندی | کار با اعداد | استدلال ریاضی</t>
+          <t>بیان شفاهی | وضوح گفتار | درک شفاهی | درک کتبی | بیان کتبی | تشخیص گفتار | استدلال استقرایی | استدلال قیاسی | روانی ایده‌ها | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | اصالت | انعطاف‌پذیری دسته‌بندی | توانایی عددی | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>نمایندگان و کارشناسان فروش تبلیغات | مدیران تبلیغات و بازاریابی ترویجی | مدیران برنامه‌ها و کارگزاران هنرمندان، مجریان و ورزشکاران | کارشناسان تحلیل بودجه | مدیران ارشد اجرایی | مشاوران اعتباری و تسهیلات | مدیران اداری و آموزشی دانشگاه‌ها و مؤسسات آموزش عالی | مدیران مالی | مدیران جذب منابع مالی | مدیران پروژه‌های فناوری اطلاعات | مدیران صندوق‌های سرمایه‌گذاری | کارشناسان تحلیل مدیریت و روش‌ها | کارشناسان تحلیل تحقیقات بازار و بازاریابی | مدیران بازاریابی | کارشناسان برنامه‌ریزی و برگزاری همایش‌ها و رویدادها | مشاوران امور مالی فردی | مدیران روابط عمومی | کارشناسان روابط عمومی | مدیران فروش | مدیران خدمات اجتماعی و عام‌المنفعه</t>
+          <t>کارشناسان فروش فضاهای تبلیغاتی | مدیران تبلیغات و روابط ترویجی | مدیران برنامه‌ها و نمایندگان هنرمندان، مجریان و ورزشکاران | تحلیل‌گران بودجه | مدیران عامل و مدیران ارشد اجرایی | مشاوران اعتباری و مدیریت بدهی | مدیران آموزش عالی | مدیران امور مالی | مدیران جذب منابع مالی و حامیان | مدیران پروژه‌های فناوری اطلاعات | مدیران صندوق‌های سرمایه‌گذاری | کارشناسان تحلیل مدیریت و روش‌ها | کارشناسان تحلیل تحقیقات بازار و بازاریابی | مدیران بازاریابی | کارشناسان برنامه‌ریزی و برگزاری همایش‌ها و رویدادها | مشاوران مالی فردی | مدیران روابط عمومی | کارشناسان روابط عمومی | مدیران فروش | مدیران خدمات اجتماعی و خدمات مردمی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | سخن گفتن | تفکر انتقادی | نگارش | یادگیری فعال | ریاضیات | نظارت</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | تفکر انتقادی | نگارش | یادگیری فعال | ریاضیات | نظارت</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>امور کارکنان و منابع انسانی | زبان انگلیسی | خدمات مشتریان و خدمات فردی | ریاضیات | مدیریت و امور اداری | اقتصاد و حسابداری | امور اداری و دفتری | رایانه و الکترونیک | حقوق و مقررات دولتی</t>
+          <t>پرسنل و منابع انسانی | زبان انگلیسی | خدمات مشتری و شخصی | ریاضیات | مدیریت و اداره | اقتصاد و حسابداری | اداری | رایانه و الکترونیک | قانون و دولت</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | بیان کتبی | مرتب‌سازی اطلاعات | دید نزدیک | تشخیص گفتار | استدلال ریاضی | توجه انتخابی | انعطاف‌پذیری در ادراک الگوها | ابتکار و اصالت | روانی کلام و ایده‌پردازی | انعطاف‌پذیری در دسته‌بندی</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | بیان کتبی | ترتیب‌دهی اطلاعات | بینایی نزدیک | تشخیص گفتار | استدلال ریاضی | توجه انتخابی | انعطاف‌پذیری بستار | اصالت | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | مدیران خدمات اداری | کارشناسان تحلیل بودجه | مدیران ارشد اجرایی | مدیران حقوق و مزایا و جبران خدمت | مدیران انطباق و نظارت قانونی | مصاحبه‌کنندگان تعیین صلاحیت برنامه‌های حمایتی دولتی | کارشناسان و بازرسان برابری فرصت‌های شغلی | بازرسان و کارشناسان نظارت مالی | مدیران مالی | سرپرستان رده‌اول کارکنان پشتیبانی دفتری و اداری | دستیاران امور اداری و منابع انسانی، به‌جز حقوق و دستمزد و کارکرد | مدیران منابع انسانی | کارشناسان منابع انسانی | متصدیان صدور و پردازش بیمه‌نامه و خسارت | کارشناسان روابط کار و امور تشکل‌های کارگری | کارشناسان تحلیل مدیریت و روش‌ها | مدیران مراکز درمانی و خدمات بهداشتی | متصدیان امور کارکرد و حقوق و دستمزد | مدیران خدمات اجتماعی و عام‌المنفعه</t>
+          <t>حسابداران و حسابرسان | مدیران خدمات اداری و پشتیبانی | تحلیل‌گران بودجه | مدیران عامل و مدیران ارشد اجرایی | مدیران جبران خدمت و مزایا | مدیران تطبیق و نظارت مقرراتی | کارشناسان مصاحبه و احراز صلاحیت متقاضیان طرح‌های حمایتی و دولتی | کارشناسان امور انطباق و صیانت از فرصت‌های برابر استخدامی | بازرسان و ارزیابان مالی | مدیران امور مالی | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | دستیاران منابع انسانی، به جز حقوق و دستمزد و ثبت ساعات کار | مدیران منابع انسانی | کارشناسان منابع انسانی | کارمندان پردازش خسارت و بیمه‌نامه‌ها | کارشناسان روابط کار و امور تشکل‌های کارگری | کارشناسان تحلیل مدیریت و روش‌ها | مدیران خدمات درمانی و بهداشتی | کارمندان امور حقوق، دستمزد و ثبت زمان | مدیران خدمات اجتماعی و خدمات مردمی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>سخن گفتن | راهبردهای یادگیری | شنیدن فعال | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | نظارت</t>
+          <t>سخن گفتن | راهبردهای یادگیری | گوش دادن فعال | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | خدمات مشتریان و خدمات فردی | زبان انگلیسی | امور کارکنان و منابع انسانی | مدیریت و امور اداری | روان‌شناسی | ارتباطات و رسانه</t>
+          <t>آموزش و پرورش | خدمات مشتری و شخصی | زبان انگلیسی | پرسنل و منابع انسانی | مدیریت و اداره | روان‌شناسی | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | تشخیص گفتار | وضوح گفتار | دید نزدیک | روانی کلام و ایده‌پردازی | حساسیت به مسئله | استدلال قیاسی | ابتکار و اصالت | استدلال استقرایی | انعطاف‌پذیری در دسته‌بندی | مرتب‌سازی اطلاعات | دید دور | توجه انتخابی | به خاطرسپاری</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | تشخیص گفتار | وضوح گفتار | بینایی نزدیک | روانی ایده‌ها | حساسیت به مسئله | استدلال قیاسی | اصالت | استدلال استقرایی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | بینایی دور | توجه انتخابی | حفظ کردن</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>معلمان دوره‌های مهارتی و فنی‌وحرفه‌ای، متوسطه اول | مدرسان آموزش‌های فنی، مهارتی و کاربردی، آموزش عالی | معلمان دوره‌های مهارتی و فنی‌وحرفه‌ای، متوسطه دوم | مدیران آموزشی مدارس و مراکز آموزش و پرورش | مدرسان علوم تربیتی و آموزش، آموزش عالی | مدیران مراکز پیش‌دبستانی و مهدکودک | مشاوران و راهنمایان تحصیلی، شغلی و تربیتی | مربیان ورزش و آمادگی جسمانی | سرپرستان رده‌اول کارکنان حوزه تفریحات و سرگرمی، به‌جز خدمات شرط‌بندی | هماهنگ‌کنندگان برنامه‌های سلامت و تندرستی | کارشناسان آموزش بهداشت و ارتقای سلامت | مدیران منابع انسانی | کارشناسان منابع انسانی | روان‌شناسان صنعتی و سازمانی | کارشناسان هماهنگی و برنامه‌ریزی درسی | کارشناسان تحلیل مدیریت و روش‌ها | متخصصان مدیریت پروژه | مشاوران توانبخشی شغلی | مدیران آموزش و بهسازی منابع انسانی | مدرسان و معلمان خصوصی</t>
+          <t>معلمان آموزش‌های فنی و حرفه‌ای در دوره اول متوسطه | مدرسان آموزش‌های فنی و حرفه‌ای در آموزش عالی | هنرآموزان و معلمان فنی‌وحرفه‌ای و کاردانش دوره دوم متوسطه | مدیران آموزشی مقاطع ابتدایی و متوسطه | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | مدیران مراکز آموزشی و مراقبت از کودک، پیش‌دبستانی و مهدکودک | مشاوران تحصیلی، شغلی و هدایت استعدادها | مربیان ورزش و آمادگی جسمانی گروهی | سرپرستان رده‌اول کارکنان مراکز تفریحی و سرگرمی، به‌جز بازی‌های شرط‌بندی | مدیران و هماهنگ‌کننده‌های برنامه‌های سلامت و تندرستی | کارشناسان آموزش بهداشت و ارتقای سلامت | مدیران منابع انسانی | کارشناسان منابع انسانی | روان‌شناسان صنعتی و سازمانی | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | کارشناسان تحلیل مدیریت و روش‌ها | کارشناسان مدیریت پروژه | مشاوران توانبخشی | مدیران آموزش و بهسازی | معلمان خصوصی و مدرسان تقویتی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نگارش | درک مطلب | شنیدن فعال | سخن گفتن | یادگیری فعال | نظارت | ریاضیات | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | نگارش | درک مطلب | گوش دادن فعال | سخن گفتن | یادگیری فعال | نظارت | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | خدمات مشتریان و خدمات فردی | فروش و بازاریابی | ریاضیات | مدیریت و امور اداری | ارتباطات و رسانه | امور اداری و دفتری | رایانه و الکترونیک | جامعه‌شناسی و مردم‌شناسی | روان‌شناسی | اقتصاد و حسابداری</t>
+          <t>زبان انگلیسی | خدمات مشتری و شخصی | فروش و بازاریابی | ریاضیات | مدیریت و اداره | ارتباطات و رسانه | اداری | رایانه و الکترونیک | جامعه‌شناسی و انسان‌شناسی | روان‌شناسی | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>استدلال استقرایی | درک کتبی | بیان شفاهی | بیان کتبی | روانی کلام و ایده‌پردازی | استدلال قیاسی | درک شفاهی | مرتب‌سازی اطلاعات | وضوح گفتار | انعطاف‌پذیری در دسته‌بندی | دید نزدیک | حساسیت به مسئله | استدلال ریاضی | ابتکار و اصالت | تشخیص گفتار | کار با اعداد | انعطاف‌پذیری در ادراک الگوها</t>
+          <t>استدلال استقرایی | درک کتبی | بیان شفاهی | بیان کتبی | روانی ایده‌ها | استدلال قیاسی | درک شفاهی | ترتیب‌دهی اطلاعات | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | حساسیت به مسئله | استدلال ریاضی | اصالت | تشخیص گفتار | توانایی عددی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>نمایندگان و کارشناسان فروش تبلیغات | مدیران تبلیغات و بازاریابی ترویجی | کارشناسان تحلیل هوش تجاری | مدرسان علوم بازرگانی و اداری، آموزش عالی | دانشمندان علم داده | کارشناسان تحلیل ریسک مالی | کارشناسان تحلیل سرمایه‌گذاری و مالی | کارشناسان تحلیل مدیریت و روش‌ها | مدیران بازاریابی | کارشناسان فروش اینترنتی و تجارت الکترونیک | مشاوران امور مالی فردی | مدیران روابط عمومی | کارشناسان روابط عمومی | مدیران فروش | کارشناسان فروش خدمات، به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری | کارشناسان تدوین راهبرد بازاریابی موتورهای جستجو | کارشناسان فروش اوراق بهادار، کالا و خدمات مالی | کارشناسان پژوهش‌های پیمایشی و نظرسنجی | خریداران عمده و کارشناسان خرید بازرگانی، به‌جز محصولات کشاورزی | نویسندگان، مؤلفان و پدیدآورندگان محتوا</t>
+          <t>کارشناسان فروش فضاهای تبلیغاتی | مدیران تبلیغات و روابط ترویجی | تحلیل‌گران هوش تجاری | استادان علوم اداری و مدیریت، آموزش عالی | دانشمندان داده | کارشناسان ریسک مالی | تحلیل‌گران مالی و سرمایه‌گذاری | کارشناسان تحلیل مدیریت و روش‌ها | مدیران بازاریابی | کارشناسان تجارت الکترونیک و فروشگاه‌های اینترنتی | مشاوران مالی فردی | مدیران روابط عمومی | کارشناسان روابط عمومی | مدیران فروش | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری) | کارشناسان تدوین راهبرد بازاریابی موتورهای جستجو | کارشناسان فروش اوراق بهادار، کالاها و خدمات مالی | پژوهشگران پیمایشی و افکارسنجی | خریداران عمده‌فروشی و خرده‌فروشی کالاهای غیرکشاورزی | نویسندگان و پدیدآورندگان</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | یادگیری فعال | شنیدن فعال | تفکر انتقادی | سخن گفتن | نگارش | نظارت</t>
+          <t>درک مطلب | یادگیری فعال | گوش دادن فعال | تفکر انتقادی | سخن گفتن | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>فروش و بازاریابی | رایانه و الکترونیک | زبان انگلیسی | ارتباطات و رسانه | ریاضیات | خدمات مشتریان و خدمات فردی</t>
+          <t>فروش و بازاریابی | رایانه و الکترونیک | زبان انگلیسی | ارتباطات و رسانه | ریاضیات | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | روانی کلام و ایده‌پردازی | حساسیت به مسئله | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | مرتب‌سازی اطلاعات | استدلال استقرایی | انعطاف‌پذیری در دسته‌بندی | ابتکار و اصالت | دید نزدیک | انعطاف‌پذیری در ادراک الگوها | توجه انتخابی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | روانی ایده‌ها | حساسیت به مسئله | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | ترتیب‌دهی اطلاعات | استدلال استقرایی | انعطاف‌پذیری دسته‌بندی | اصالت | بینایی نزدیک | انعطاف‌پذیری بستار | توجه انتخابی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>نمایندگان و کارشناسان فروش تبلیغات | مدیران تبلیغات و بازاریابی ترویجی | کارشناسان تحلیل هوش تجاری | برنامه‌نویسان کامپیوتر | کارشناسان تحلیل سیستم‌های کامپیوتری | دانشمندان علم داده | متخصصان مدیریت اسناد و مدارک | کارشناسان تحلیل مدیریت و روش‌ها | کارشناسان تحلیل تحقیقات بازار و بازاریابی | مدیران بازاریابی | کارشناسان فروش اینترنتی و تجارت الکترونیک | مدیران روابط عمومی | کارشناسان روابط عمومی | مدیران فروش | کارشناسان فروش خدمات، به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری | توسعه‌دهندگان نرم‌افزار | مدیران و راهبران وب‌سایت | توسعه‌دهندگان وب | طراحان رابط کاربری وب و ابزارهای دیجیتال | نویسندگان، مؤلفان و پدیدآورندگان محتوا</t>
+          <t>کارشناسان فروش فضاهای تبلیغاتی | مدیران تبلیغات و روابط ترویجی | تحلیل‌گران هوش تجاری | برنامه‌نویسان کامپیوتر | تحلیل‌گران سیستم‌های کامپیوتری | دانشمندان داده | کارشناسان مدیریت اسناد و مدارک | کارشناسان تحلیل مدیریت و روش‌ها | کارشناسان تحلیل تحقیقات بازار و بازاریابی | مدیران بازاریابی | کارشناسان تجارت الکترونیک و فروشگاه‌های اینترنتی | مدیران روابط عمومی | کارشناسان روابط عمومی | مدیران فروش | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری) | توسعه‌دهندگان نرم‌افزار | مدیران وب | توسعه‌دهندگان وب | طراحان وب و رابط‌های دیجیتال | نویسندگان و پدیدآورندگان</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>مدیریت و امور اداری | زبان انگلیسی | خدمات مشتریان و خدمات فردی | اقتصاد و حسابداری | رایانه و الکترونیک | ریاضیات | امور کارکنان و منابع انسانی | حقوق و مقررات دولتی | فروش و بازاریابی | ارتباطات و رسانه</t>
+          <t>مدیریت و اداره | زبان انگلیسی | خدمات مشتری و شخصی | اقتصاد و حسابداری | رایانه و الکترونیک | ریاضیات | پرسنل و منابع انسانی | قانون و دولت | فروش و بازاریابی | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | حساسیت به مسئله | دید نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری در دسته‌بندی | روانی کلام و ایده‌پردازی | ابتکار و اصالت | توجه انتخابی | اشتراک زمانی | تجسم فضایی | به خاطرسپاری | استدلال ریاضی | کار با اعداد | سرعت ادراک | انعطاف‌پذیری در ادراک الگوها</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن | استدلال ریاضی | توانایی عددی | سرعت ادراکی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>کارشناسان تحلیل مدیریت و روش‌ها | متخصصان مدیریت پروژه | کارشناسان برنامه‌ریزی تداوم کسب‌وکار | کارشناسان پایداری و توسعه پایدار | کارشناسان مدیریت امنیت | کارشناسان فروش اینترنتی و تجارت الکترونیک | کارشناسان لجستیک و زنجیره تأمین | کارشناسان تحلیل امور لجستیک | کارشناسان ارزیابی و انطباق قانونی | کارشناسان برآورد و متره هزینه‌ها | کارشناسان منابع انسانی | کارشناسان آموزش و توسعه منابع انسانی | کارشناسان برنامه‌ریزی و برگزاری همایش‌ها و رویدادها | کارشناسان تحلیل تحقیقات بازار و بازاریابی | کارشناسان جذب منابع مالی و حامی | کارشناسان روابط کار و امور تشکل‌های کارگری | کارشناسان جبران خدمت، مزایا و طبقه‌بندی مشاغل | مأموران خرید و تدارکات، به‌جز عمده‌فروشی، خرده‌فروشی و کشاورزی | مدیران اجرایی و مدیران عملیات | حسابداران و حسابرسان</t>
+          <t>کارشناسان تحلیل مدیریت و روش‌ها | کارشناسان مدیریت پروژه | کارشناسان برنامه‌ریزی تداوم کسب‌وکار | کارشناسان پایداری و توسعه پایدار | کارشناسان مدیریت حراست و امنیت فیزیکی | کارشناسان تجارت الکترونیک و فروشگاه‌های اینترنتی | کارشناسان لجستیک و مدیریت زنجیره تأمین | تحلیل‌گران لجستیک و فرایند توزیع | کارشناسان پایش انطباق و بازرسی مقرراتی | کارشناسان برآورد هزینه و مترورها | کارشناسان منابع انسانی | کارشناسان آموزش و توسعه منابع انسانی | کارشناسان برنامه‌ریزی و برگزاری همایش‌ها و رویدادها | کارشناسان تحلیل تحقیقات بازار و بازاریابی | کارشناسان جذب منابع مالی و حامی | کارشناسان روابط کار و امور تشکل‌های کارگری | کارشناسان جبران خدمت، مزایا و طبقه‌بندی مشاغل | کارشناسان خرید و امور قراردادها | مدیران کل و مدیران عملیات | حسابداران و حسابرسان</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | درک مطلب | یادگیری فعال | سخن گفتن | نگارش | نظارت | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | تفکر انتقادی | درک مطلب | یادگیری فعال | سخن گفتن | نگارش | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | ایمنی و امنیت عمومی | مدیریت و امور اداری | خدمات مشتریان و خدمات فردی | رایانه و الکترونیک | آموزش و تدریس | ارتباطات و رسانه | امور اداری و دفتری</t>
+          <t>زبان انگلیسی | ایمنی و امنیت عمومی | مدیریت و اداره | خدمات مشتری و شخصی | رایانه و الکترونیک | آموزش و پرورش | ارتباطات و رسانه | اداری</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | استدلال استقرایی | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | مرتب‌سازی اطلاعات | روانی کلام و ایده‌پردازی | تشخیص گفتار | وضوح گفتار | دید نزدیک | ابتکار و اصالت | انعطاف‌پذیری در ادراک الگوها | انعطاف‌پذیری در دسته‌بندی | توجه انتخابی</t>
+          <t>حساسیت به مسئله | استدلال استقرایی | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | ترتیب‌دهی اطلاعات | روانی ایده‌ها | تشخیص گفتار | وضوح گفتار | بینایی نزدیک | اصالت | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری | کارشناسان تحلیل هوش تجاری | مدیران ارشد پایداری سازمانی | مدیران انطباق و نظارت قانونی | کارشناسان تحلیل سیستم‌های کامپیوتری | مهندسان و معماران سیستم‌های کامپیوتری | مدیران فناوری اطلاعات و سیستم‌های کامپیوتری | مدیران پایگاه داده | متخصصان مدیریت اسناد و مدارک | مدیران مدیریت بحران | کارشناسان تحلیل ریسک مالی | کارشناسان تحلیل امنیت اطلاعات | مهندسان امنیت اطلاعات | مدیران پروژه‌های فناوری اطلاعات | کارشناسان لجستیک و زنجیره تأمین | کارشناسان تحلیل امور لجستیک | کارشناسان تحلیل مدیریت و روش‌ها | متخصصان مدیریت پروژه | کارشناسان مدیریت امنیت | مدیران حراست و امنیت</t>
+          <t>مدیران خدمات اداری و پشتیبانی | تحلیل‌گران هوش تجاری | مدیران ارشد پایداری سازمانی | مدیران تطبیق و نظارت مقرراتی | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | مدیران فناوری اطلاعات و سیستم‌های رایانه‌ای | مدیران پایگاه داده | کارشناسان مدیریت اسناد و مدارک | مدیران مدیریت بحران و پدافند غیرعامل | کارشناسان ریسک مالی | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | مدیران پروژه‌های فناوری اطلاعات | کارشناسان لجستیک و مدیریت زنجیره تأمین | تحلیل‌گران لجستیک و فرایند توزیع | کارشناسان تحلیل مدیریت و روش‌ها | کارشناسان مدیریت پروژه | کارشناسان مدیریت حراست و امنیت فیزیکی | مدیران حراست و انتظامات</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>سخن گفتن | نگارش | درک مطلب | شنیدن فعال | تفکر انتقادی | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>سخن گفتن | نگارش | درک مطلب | گوش دادن فعال | تفکر انتقادی | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>مدیریت و امور اداری | حقوق و مقررات دولتی | زبان انگلیسی | آموزش و تدریس | ساختمان و سازه | خدمات مشتریان و خدمات فردی | ارتباطات و رسانه | مهندسی و فناوری</t>
+          <t>مدیریت و اداره | قانون و دولت | زبان انگلیسی | آموزش و پرورش | ساختمان و ساخت‌وساز | خدمات مشتری و شخصی | ارتباطات و رسانه | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک کتبی | بیان کتبی | درک شفاهی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | حساسیت به مسئله | مرتب‌سازی اطلاعات | ابتکار و اصالت | تشخیص گفتار | روانی کلام و ایده‌پردازی | انعطاف‌پذیری در دسته‌بندی | دید نزدیک | استدلال ریاضی</t>
+          <t>درک کتبی | بیان کتبی | درک شفاهی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | حساسیت به مسئله | ترتیب‌دهی اطلاعات | اصالت | تشخیص گفتار | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>مدیران معماری و مهندسی | مدیران فناوری و تولید سوخت‌های زیستی | مدیران پروژه‌های بهسازی و احیای اراضی صنعتی آسیب‌دیده | مدیران ارشد پایداری سازمانی | کارشناسان تحلیل سیاست‌های تغییر اقلیم | دانشمندان حفاظت از منابع طبیعی | کارشناسان ممیزی انرژی | مهندسان انرژی، به‌جز باد و خورشید | مهندسان محیط‌زیست | کارشناسان برنامه‌ریزی بهسازی و بازسازی محیط‌زیست | دانشمندان و متخصصان محیط‌زیست و سلامت | بوم‌شناسان و اکولوژیست‌های صنعتی | مدیران پروژه‌های فناوری اطلاعات | مهندسان معمار منظر | کارشناسان تحلیل مدیریت و روش‌ها | متخصصان مدیریت پروژه | کارشناسان فروش و ارزیابی سیستم‌های خورشیدی | مهندسان شهرسازی و برنامه‌ریزی شهری و منطقه‌ای | کارشناسان و متخصصان منابع آب | مدیران توسعه پروژه‌های انرژی بادی</t>
+          <t>مدیران فنی و مهندسی و معماری | مدیران توسعه محصول و فناوری زیست‌سوخت | مدیران و کارشناسان احیا و بازسازی اراضی قهوه‌ای و آلوده | مدیران ارشد پایداری سازمانی | تحلیل‌گران خط‌مشی تغییر اقلیم | دانشمندان حفاظت از منابع طبیعی | ممیزان انرژی | مهندسان انرژی، به‌جز بادی و خورشیدی | مهندسان محیط‌زیست | برنامه‌ریزان احیای محیط زیست | کارشناسان و متخصصان علوم محیطی (شامل بهداشت) | بوم‌شناسان صنعتی | مدیران پروژه‌های فناوری اطلاعات | مهندسان معمار منظر | کارشناسان تحلیل مدیریت و روش‌ها | کارشناسان مدیریت پروژه | کارشناسان فروش و ارزیابان سامانه‌های خورشیدی | برنامه‌ریزان شهری و منطقه‌ای | کارشناسان و متخصصان مدیریت منابع آب | مدیران توسعه پروژه‌های انرژی بادی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
